--- a/artfynd/A 31817-2025 artfynd.xlsx
+++ b/artfynd/A 31817-2025 artfynd.xlsx
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128794519</v>
+        <v>128794499</v>
       </c>
       <c r="B4" t="n">
-        <v>79089</v>
+        <v>80194</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511436</v>
+        <v>511149</v>
       </c>
       <c r="R4" t="n">
-        <v>7106614</v>
+        <v>7106300</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128794492</v>
+        <v>128794519</v>
       </c>
       <c r="B5" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>510773</v>
+        <v>511436</v>
       </c>
       <c r="R5" t="n">
-        <v>7106391</v>
+        <v>7106614</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,7 +1046,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128794499</v>
+        <v>128794477</v>
       </c>
       <c r="B7" t="n">
-        <v>80194</v>
+        <v>91825</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>2062</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511149</v>
+        <v>510687</v>
       </c>
       <c r="R7" t="n">
-        <v>7106300</v>
+        <v>7106478</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1272,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128794477</v>
+        <v>128794492</v>
       </c>
       <c r="B8" t="n">
-        <v>91824</v>
+        <v>57689</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510687</v>
+        <v>510773</v>
       </c>
       <c r="R8" t="n">
-        <v>7106478</v>
+        <v>7106391</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1343,6 +1338,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1372,7 +1372,7 @@
         <v>128794485</v>
       </c>
       <c r="B9" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1466,10 +1466,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128794480</v>
+        <v>128794479</v>
       </c>
       <c r="B10" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>510843</v>
+        <v>510847</v>
       </c>
       <c r="R10" t="n">
-        <v>7106605</v>
+        <v>7106602</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128794479</v>
+        <v>128794480</v>
       </c>
       <c r="B11" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>510847</v>
+        <v>510843</v>
       </c>
       <c r="R11" t="n">
-        <v>7106602</v>
+        <v>7106605</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1660,7 +1660,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128794506</v>
+        <v>128794501</v>
       </c>
       <c r="B12" t="n">
         <v>80194</v>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>510758</v>
+        <v>511349</v>
       </c>
       <c r="R12" t="n">
-        <v>7106421</v>
+        <v>7106644</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128794509</v>
+        <v>128794506</v>
       </c>
       <c r="B13" t="n">
-        <v>91462</v>
+        <v>80194</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510663</v>
+        <v>510758</v>
       </c>
       <c r="R13" t="n">
-        <v>7106445</v>
+        <v>7106421</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128794481</v>
+        <v>128794509</v>
       </c>
       <c r="B14" t="n">
-        <v>91466</v>
+        <v>91463</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>510842</v>
+        <v>510663</v>
       </c>
       <c r="R14" t="n">
-        <v>7106609</v>
+        <v>7106445</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1954,7 +1954,7 @@
         <v>128794482</v>
       </c>
       <c r="B15" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128794501</v>
+        <v>128794481</v>
       </c>
       <c r="B16" t="n">
-        <v>80194</v>
+        <v>91467</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,21 +2059,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511349</v>
+        <v>510842</v>
       </c>
       <c r="R16" t="n">
-        <v>7106644</v>
+        <v>7106609</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2148,7 +2148,7 @@
         <v>128794478</v>
       </c>
       <c r="B17" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2242,10 +2242,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128794488</v>
+        <v>128794524</v>
       </c>
       <c r="B18" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2253,21 +2253,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>510695</v>
+        <v>510700</v>
       </c>
       <c r="R18" t="n">
-        <v>7106401</v>
+        <v>7106468</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Granska rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2344,10 +2344,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128794524</v>
+        <v>128794488</v>
       </c>
       <c r="B19" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2355,21 +2355,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>510700</v>
+        <v>510695</v>
       </c>
       <c r="R19" t="n">
-        <v>7106468</v>
+        <v>7106401</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2419,7 +2419,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Granska rikligt</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2648,7 +2648,7 @@
         <v>128794498</v>
       </c>
       <c r="B22" t="n">
-        <v>91762</v>
+        <v>91763</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         <v>128794476</v>
       </c>
       <c r="B23" t="n">
-        <v>91824</v>
+        <v>91825</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2840,10 +2840,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128794517</v>
+        <v>128794515</v>
       </c>
       <c r="B24" t="n">
-        <v>79089</v>
+        <v>91485</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2851,21 +2851,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2875,10 +2875,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>511489</v>
+        <v>511143</v>
       </c>
       <c r="R24" t="n">
-        <v>7106495</v>
+        <v>7106625</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2911,11 +2911,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3039,10 +3034,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128794515</v>
+        <v>128794517</v>
       </c>
       <c r="B26" t="n">
-        <v>91484</v>
+        <v>79089</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3050,21 +3045,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3074,10 +3069,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>511143</v>
+        <v>511489</v>
       </c>
       <c r="R26" t="n">
-        <v>7106625</v>
+        <v>7106495</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3110,6 +3105,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3136,10 +3136,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128794511</v>
+        <v>128794516</v>
       </c>
       <c r="B27" t="n">
-        <v>91484</v>
+        <v>79089</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3147,21 +3147,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>511450</v>
+        <v>511210</v>
       </c>
       <c r="R27" t="n">
-        <v>7106469</v>
+        <v>7106268</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3207,6 +3207,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3233,10 +3238,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128794486</v>
+        <v>128794503</v>
       </c>
       <c r="B28" t="n">
-        <v>91466</v>
+        <v>80194</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3244,21 +3249,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3268,10 +3273,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>510777</v>
+        <v>510694</v>
       </c>
       <c r="R28" t="n">
-        <v>7106379</v>
+        <v>7106493</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3330,10 +3335,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128794516</v>
+        <v>128794486</v>
       </c>
       <c r="B29" t="n">
-        <v>79089</v>
+        <v>91467</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3341,21 +3346,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3365,10 +3370,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>511210</v>
+        <v>510777</v>
       </c>
       <c r="R29" t="n">
-        <v>7106268</v>
+        <v>7106379</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3401,11 +3406,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3432,10 +3432,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128794503</v>
+        <v>128794511</v>
       </c>
       <c r="B30" t="n">
-        <v>80194</v>
+        <v>91485</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3443,21 +3443,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>510694</v>
+        <v>511450</v>
       </c>
       <c r="R30" t="n">
-        <v>7106493</v>
+        <v>7106469</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3532,7 +3532,7 @@
         <v>128794497</v>
       </c>
       <c r="B31" t="n">
-        <v>91920</v>
+        <v>91921</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3723,10 +3723,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128794521</v>
+        <v>128794505</v>
       </c>
       <c r="B33" t="n">
-        <v>79089</v>
+        <v>80194</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3734,21 +3734,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>511134</v>
+        <v>510689</v>
       </c>
       <c r="R33" t="n">
-        <v>7106628</v>
+        <v>7106463</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3794,11 +3794,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3825,10 +3820,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128794505</v>
+        <v>128794521</v>
       </c>
       <c r="B34" t="n">
-        <v>80194</v>
+        <v>79089</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3836,21 +3831,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3860,10 +3855,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>510689</v>
+        <v>511134</v>
       </c>
       <c r="R34" t="n">
-        <v>7106463</v>
+        <v>7106628</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3896,6 +3891,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4328,10 +4328,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128794523</v>
+        <v>128794513</v>
       </c>
       <c r="B39" t="n">
-        <v>79089</v>
+        <v>91485</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4339,21 +4339,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4363,10 +4363,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>510685</v>
+        <v>511247</v>
       </c>
       <c r="R39" t="n">
-        <v>7106500</v>
+        <v>7106612</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4425,10 +4425,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128794513</v>
+        <v>128794523</v>
       </c>
       <c r="B40" t="n">
-        <v>91484</v>
+        <v>79089</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4436,21 +4436,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4460,10 +4460,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>511247</v>
+        <v>510685</v>
       </c>
       <c r="R40" t="n">
-        <v>7106612</v>
+        <v>7106500</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4522,32 +4522,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128794510</v>
+        <v>128794526</v>
       </c>
       <c r="B41" t="n">
-        <v>91480</v>
+        <v>89445</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1204</v>
+        <v>236437</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Brun klibbskivling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Limacella glioderma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Maire</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4557,10 +4557,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>510841</v>
+        <v>510763</v>
       </c>
       <c r="R41" t="n">
-        <v>7106597</v>
+        <v>7106387</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4622,7 +4622,7 @@
         <v>128794484</v>
       </c>
       <c r="B42" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4716,10 +4716,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128794512</v>
+        <v>128794510</v>
       </c>
       <c r="B43" t="n">
-        <v>91484</v>
+        <v>91481</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4727,21 +4727,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4751,10 +4751,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>511307</v>
+        <v>510841</v>
       </c>
       <c r="R43" t="n">
-        <v>7106634</v>
+        <v>7106597</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4813,32 +4813,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128794526</v>
+        <v>128794512</v>
       </c>
       <c r="B44" t="n">
-        <v>89445</v>
+        <v>91485</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>236437</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brun klibbskivling</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Limacella glioderma</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Maire</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4848,10 +4848,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>510763</v>
+        <v>511307</v>
       </c>
       <c r="R44" t="n">
-        <v>7106387</v>
+        <v>7106634</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 31817-2025 artfynd.xlsx
+++ b/artfynd/A 31817-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128794507</v>
+        <v>128794508</v>
       </c>
       <c r="B2" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510771</v>
+        <v>510782</v>
       </c>
       <c r="R2" t="n">
-        <v>7106380</v>
+        <v>7106356</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128794508</v>
+        <v>128794507</v>
       </c>
       <c r="B3" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510782</v>
+        <v>510771</v>
       </c>
       <c r="R3" t="n">
-        <v>7106356</v>
+        <v>7106380</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128794499</v>
+        <v>128794477</v>
       </c>
       <c r="B4" t="n">
-        <v>80194</v>
+        <v>91852</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>2062</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511149</v>
+        <v>510687</v>
       </c>
       <c r="R4" t="n">
-        <v>7106300</v>
+        <v>7106478</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
         <v>128794519</v>
       </c>
       <c r="B5" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>128794520</v>
       </c>
       <c r="B6" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1170,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128794477</v>
+        <v>128794492</v>
       </c>
       <c r="B7" t="n">
-        <v>91825</v>
+        <v>57716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510687</v>
+        <v>510773</v>
       </c>
       <c r="R7" t="n">
-        <v>7106478</v>
+        <v>7106391</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1241,6 +1241,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,10 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128794492</v>
+        <v>128794499</v>
       </c>
       <c r="B8" t="n">
-        <v>57689</v>
+        <v>80221</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1283,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510773</v>
+        <v>511149</v>
       </c>
       <c r="R8" t="n">
-        <v>7106391</v>
+        <v>7106300</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1338,11 +1343,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1372,7 +1372,7 @@
         <v>128794485</v>
       </c>
       <c r="B9" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>128794479</v>
       </c>
       <c r="B10" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>128794480</v>
       </c>
       <c r="B11" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>128794501</v>
       </c>
       <c r="B12" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>128794506</v>
       </c>
       <c r="B13" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>128794509</v>
       </c>
       <c r="B14" t="n">
-        <v>91463</v>
+        <v>91490</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>128794482</v>
       </c>
       <c r="B15" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>128794481</v>
       </c>
       <c r="B16" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>128794478</v>
       </c>
       <c r="B17" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>128794524</v>
       </c>
       <c r="B18" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>128794488</v>
       </c>
       <c r="B19" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>128794496</v>
       </c>
       <c r="B20" t="n">
-        <v>80195</v>
+        <v>80222</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>128794491</v>
       </c>
       <c r="B21" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         <v>128794498</v>
       </c>
       <c r="B22" t="n">
-        <v>91763</v>
+        <v>91790</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         <v>128794476</v>
       </c>
       <c r="B23" t="n">
-        <v>91825</v>
+        <v>91852</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2840,10 +2840,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128794515</v>
+        <v>128794525</v>
       </c>
       <c r="B24" t="n">
-        <v>91485</v>
+        <v>88894</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2851,21 +2851,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2875,10 +2875,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>511143</v>
+        <v>510696</v>
       </c>
       <c r="R24" t="n">
-        <v>7106625</v>
+        <v>7106461</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128794525</v>
+        <v>128794515</v>
       </c>
       <c r="B25" t="n">
-        <v>88867</v>
+        <v>91512</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2948,21 +2948,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>510696</v>
+        <v>511143</v>
       </c>
       <c r="R25" t="n">
-        <v>7106461</v>
+        <v>7106625</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3037,7 +3037,7 @@
         <v>128794517</v>
       </c>
       <c r="B26" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128794516</v>
+        <v>128794486</v>
       </c>
       <c r="B27" t="n">
-        <v>79089</v>
+        <v>91494</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3147,21 +3147,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>511210</v>
+        <v>510777</v>
       </c>
       <c r="R27" t="n">
-        <v>7106268</v>
+        <v>7106379</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3207,11 +3207,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3238,10 +3233,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128794503</v>
+        <v>128794511</v>
       </c>
       <c r="B28" t="n">
-        <v>80194</v>
+        <v>91512</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3249,21 +3244,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3273,10 +3268,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>510694</v>
+        <v>511450</v>
       </c>
       <c r="R28" t="n">
-        <v>7106493</v>
+        <v>7106469</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3335,10 +3330,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128794486</v>
+        <v>128794516</v>
       </c>
       <c r="B29" t="n">
-        <v>91467</v>
+        <v>79116</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3346,21 +3341,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3370,10 +3365,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>510777</v>
+        <v>511210</v>
       </c>
       <c r="R29" t="n">
-        <v>7106379</v>
+        <v>7106268</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3406,6 +3401,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3432,10 +3432,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128794511</v>
+        <v>128794503</v>
       </c>
       <c r="B30" t="n">
-        <v>91485</v>
+        <v>80221</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3443,21 +3443,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>511450</v>
+        <v>510694</v>
       </c>
       <c r="R30" t="n">
-        <v>7106469</v>
+        <v>7106493</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3532,7 +3532,7 @@
         <v>128794497</v>
       </c>
       <c r="B31" t="n">
-        <v>91921</v>
+        <v>91948</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>128794502</v>
       </c>
       <c r="B32" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3723,10 +3723,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128794505</v>
+        <v>128794521</v>
       </c>
       <c r="B33" t="n">
-        <v>80194</v>
+        <v>79116</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3734,21 +3734,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>510689</v>
+        <v>511134</v>
       </c>
       <c r="R33" t="n">
-        <v>7106463</v>
+        <v>7106628</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3794,6 +3794,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3820,10 +3825,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128794521</v>
+        <v>128794505</v>
       </c>
       <c r="B34" t="n">
-        <v>79089</v>
+        <v>80221</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3831,21 +3836,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3855,10 +3860,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>511134</v>
+        <v>510689</v>
       </c>
       <c r="R34" t="n">
-        <v>7106628</v>
+        <v>7106463</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3891,11 +3896,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3925,7 +3925,7 @@
         <v>128794504</v>
       </c>
       <c r="B35" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>128794489</v>
       </c>
       <c r="B36" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>128794495</v>
       </c>
       <c r="B37" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         <v>128794500</v>
       </c>
       <c r="B38" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>128794513</v>
       </c>
       <c r="B39" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>128794523</v>
       </c>
       <c r="B40" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4522,32 +4522,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128794526</v>
+        <v>128794512</v>
       </c>
       <c r="B41" t="n">
-        <v>89445</v>
+        <v>91512</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>236437</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Brun klibbskivling</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Limacella glioderma</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Maire</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4557,10 +4557,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>510763</v>
+        <v>511307</v>
       </c>
       <c r="R41" t="n">
-        <v>7106387</v>
+        <v>7106634</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4619,32 +4619,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128794484</v>
+        <v>128794526</v>
       </c>
       <c r="B42" t="n">
-        <v>91467</v>
+        <v>89472</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>236437</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brun klibbskivling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Limacella glioderma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Maire</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4654,10 +4654,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>510684</v>
+        <v>510763</v>
       </c>
       <c r="R42" t="n">
-        <v>7106476</v>
+        <v>7106387</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4716,10 +4716,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128794510</v>
+        <v>128794484</v>
       </c>
       <c r="B43" t="n">
-        <v>91481</v>
+        <v>91494</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4727,21 +4727,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4751,10 +4751,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>510841</v>
+        <v>510684</v>
       </c>
       <c r="R43" t="n">
-        <v>7106597</v>
+        <v>7106476</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4813,10 +4813,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128794512</v>
+        <v>128794510</v>
       </c>
       <c r="B44" t="n">
-        <v>91485</v>
+        <v>91508</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4824,21 +4824,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4848,10 +4848,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>511307</v>
+        <v>510841</v>
       </c>
       <c r="R44" t="n">
-        <v>7106634</v>
+        <v>7106597</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 31817-2025 artfynd.xlsx
+++ b/artfynd/A 31817-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128794508</v>
+        <v>128794507</v>
       </c>
       <c r="B2" t="n">
         <v>80221</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510782</v>
+        <v>510771</v>
       </c>
       <c r="R2" t="n">
-        <v>7106356</v>
+        <v>7106380</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128794507</v>
+        <v>128794508</v>
       </c>
       <c r="B3" t="n">
         <v>80221</v>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510771</v>
+        <v>510782</v>
       </c>
       <c r="R3" t="n">
-        <v>7106380</v>
+        <v>7106356</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128794477</v>
+        <v>128794499</v>
       </c>
       <c r="B4" t="n">
-        <v>91852</v>
+        <v>80221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2062</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510687</v>
+        <v>511149</v>
       </c>
       <c r="R4" t="n">
-        <v>7106478</v>
+        <v>7106300</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1170,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128794492</v>
+        <v>128794477</v>
       </c>
       <c r="B7" t="n">
-        <v>57716</v>
+        <v>91852</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510773</v>
+        <v>510687</v>
       </c>
       <c r="R7" t="n">
-        <v>7106391</v>
+        <v>7106478</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1241,11 +1241,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1272,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128794499</v>
+        <v>128794492</v>
       </c>
       <c r="B8" t="n">
-        <v>80221</v>
+        <v>57716</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511149</v>
+        <v>510773</v>
       </c>
       <c r="R8" t="n">
-        <v>7106300</v>
+        <v>7106391</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1343,6 +1338,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128794506</v>
+        <v>128794509</v>
       </c>
       <c r="B13" t="n">
-        <v>80221</v>
+        <v>91490</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510758</v>
+        <v>510663</v>
       </c>
       <c r="R13" t="n">
-        <v>7106421</v>
+        <v>7106445</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128794509</v>
+        <v>128794482</v>
       </c>
       <c r="B14" t="n">
-        <v>91490</v>
+        <v>91494</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>510663</v>
+        <v>510816</v>
       </c>
       <c r="R14" t="n">
-        <v>7106445</v>
+        <v>7106613</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1951,7 +1951,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128794482</v>
+        <v>128794481</v>
       </c>
       <c r="B15" t="n">
         <v>91494</v>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>510816</v>
+        <v>510842</v>
       </c>
       <c r="R15" t="n">
-        <v>7106613</v>
+        <v>7106609</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,7 +2048,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128794481</v>
+        <v>128794478</v>
       </c>
       <c r="B16" t="n">
         <v>91494</v>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>510842</v>
+        <v>511159</v>
       </c>
       <c r="R16" t="n">
-        <v>7106609</v>
+        <v>7106615</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,10 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128794478</v>
+        <v>128794506</v>
       </c>
       <c r="B17" t="n">
-        <v>91494</v>
+        <v>80221</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,21 +2156,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511159</v>
+        <v>510758</v>
       </c>
       <c r="R17" t="n">
-        <v>7106615</v>
+        <v>7106421</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2446,10 +2446,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128794496</v>
+        <v>128794491</v>
       </c>
       <c r="B20" t="n">
-        <v>80222</v>
+        <v>57716</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2457,21 +2457,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511485</v>
+        <v>510658</v>
       </c>
       <c r="R20" t="n">
-        <v>7106629</v>
+        <v>7106454</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2517,6 +2517,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2543,10 +2548,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128794491</v>
+        <v>128794496</v>
       </c>
       <c r="B21" t="n">
-        <v>57716</v>
+        <v>80222</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2554,21 +2559,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2578,10 +2583,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>510658</v>
+        <v>511485</v>
       </c>
       <c r="R21" t="n">
-        <v>7106454</v>
+        <v>7106629</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2614,11 +2619,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3330,10 +3330,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128794516</v>
+        <v>128794503</v>
       </c>
       <c r="B29" t="n">
-        <v>79116</v>
+        <v>80221</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3341,21 +3341,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>511210</v>
+        <v>510694</v>
       </c>
       <c r="R29" t="n">
-        <v>7106268</v>
+        <v>7106493</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3401,11 +3401,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3432,10 +3427,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128794503</v>
+        <v>128794516</v>
       </c>
       <c r="B30" t="n">
-        <v>80221</v>
+        <v>79116</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3443,21 +3438,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3467,10 +3462,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>510694</v>
+        <v>511210</v>
       </c>
       <c r="R30" t="n">
-        <v>7106493</v>
+        <v>7106268</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3503,6 +3498,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3723,10 +3723,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128794521</v>
+        <v>128794505</v>
       </c>
       <c r="B33" t="n">
-        <v>79116</v>
+        <v>80221</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3734,21 +3734,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>511134</v>
+        <v>510689</v>
       </c>
       <c r="R33" t="n">
-        <v>7106628</v>
+        <v>7106463</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3794,11 +3794,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3825,10 +3820,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128794505</v>
+        <v>128794521</v>
       </c>
       <c r="B34" t="n">
-        <v>80221</v>
+        <v>79116</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3836,21 +3831,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3860,10 +3855,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>510689</v>
+        <v>511134</v>
       </c>
       <c r="R34" t="n">
-        <v>7106463</v>
+        <v>7106628</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3896,6 +3891,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4522,10 +4522,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128794512</v>
+        <v>128794484</v>
       </c>
       <c r="B41" t="n">
-        <v>91512</v>
+        <v>91494</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4533,21 +4533,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4557,10 +4557,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>511307</v>
+        <v>510684</v>
       </c>
       <c r="R41" t="n">
-        <v>7106634</v>
+        <v>7106476</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4619,32 +4619,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128794526</v>
+        <v>128794510</v>
       </c>
       <c r="B42" t="n">
-        <v>89472</v>
+        <v>91508</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>236437</v>
+        <v>1204</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brun klibbskivling</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Limacella glioderma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Maire</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4654,10 +4654,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>510763</v>
+        <v>510841</v>
       </c>
       <c r="R42" t="n">
-        <v>7106387</v>
+        <v>7106597</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4716,10 +4716,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128794484</v>
+        <v>128794512</v>
       </c>
       <c r="B43" t="n">
-        <v>91494</v>
+        <v>91512</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4727,21 +4727,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4751,10 +4751,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>510684</v>
+        <v>511307</v>
       </c>
       <c r="R43" t="n">
-        <v>7106476</v>
+        <v>7106634</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4813,32 +4813,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128794510</v>
+        <v>128794526</v>
       </c>
       <c r="B44" t="n">
-        <v>91508</v>
+        <v>89472</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1204</v>
+        <v>236437</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Brun klibbskivling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Limacella glioderma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Maire</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4848,10 +4848,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>510841</v>
+        <v>510763</v>
       </c>
       <c r="R44" t="n">
-        <v>7106597</v>
+        <v>7106387</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 31817-2025 artfynd.xlsx
+++ b/artfynd/A 31817-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128794507</v>
       </c>
       <c r="B2" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128794508</v>
       </c>
       <c r="B3" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -874,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128794499</v>
+        <v>128794477</v>
       </c>
       <c r="B4" t="n">
-        <v>80221</v>
+        <v>91857</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>2062</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511149</v>
+        <v>510687</v>
       </c>
       <c r="R4" t="n">
-        <v>7106300</v>
+        <v>7106478</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128794519</v>
+        <v>128794499</v>
       </c>
       <c r="B5" t="n">
-        <v>79116</v>
+        <v>80225</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511436</v>
+        <v>511149</v>
       </c>
       <c r="R5" t="n">
-        <v>7106614</v>
+        <v>7106300</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1042,11 +1042,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128794520</v>
+        <v>128794519</v>
       </c>
       <c r="B6" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1108,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511309</v>
+        <v>511436</v>
       </c>
       <c r="R6" t="n">
-        <v>7106636</v>
+        <v>7106614</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,6 +1139,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1170,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128794477</v>
+        <v>128794520</v>
       </c>
       <c r="B7" t="n">
-        <v>91852</v>
+        <v>79120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510687</v>
+        <v>511309</v>
       </c>
       <c r="R7" t="n">
-        <v>7106478</v>
+        <v>7106636</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1372,7 +1372,7 @@
         <v>128794485</v>
       </c>
       <c r="B9" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>128794479</v>
       </c>
       <c r="B10" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>128794480</v>
       </c>
       <c r="B11" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>128794501</v>
       </c>
       <c r="B12" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128794509</v>
+        <v>128794506</v>
       </c>
       <c r="B13" t="n">
-        <v>91490</v>
+        <v>80225</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510663</v>
+        <v>510758</v>
       </c>
       <c r="R13" t="n">
-        <v>7106445</v>
+        <v>7106421</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128794482</v>
+        <v>128794509</v>
       </c>
       <c r="B14" t="n">
-        <v>91494</v>
+        <v>91495</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>510816</v>
+        <v>510663</v>
       </c>
       <c r="R14" t="n">
-        <v>7106613</v>
+        <v>7106445</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128794481</v>
+        <v>128794482</v>
       </c>
       <c r="B15" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>510842</v>
+        <v>510816</v>
       </c>
       <c r="R15" t="n">
-        <v>7106609</v>
+        <v>7106613</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128794478</v>
+        <v>128794481</v>
       </c>
       <c r="B16" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511159</v>
+        <v>510842</v>
       </c>
       <c r="R16" t="n">
-        <v>7106615</v>
+        <v>7106609</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,10 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128794506</v>
+        <v>128794478</v>
       </c>
       <c r="B17" t="n">
-        <v>80221</v>
+        <v>91499</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,21 +2156,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>510758</v>
+        <v>511159</v>
       </c>
       <c r="R17" t="n">
-        <v>7106421</v>
+        <v>7106615</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2245,7 +2245,7 @@
         <v>128794524</v>
       </c>
       <c r="B18" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2446,10 +2446,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128794491</v>
+        <v>128794496</v>
       </c>
       <c r="B20" t="n">
-        <v>57716</v>
+        <v>80226</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2457,21 +2457,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>510658</v>
+        <v>511485</v>
       </c>
       <c r="R20" t="n">
-        <v>7106454</v>
+        <v>7106629</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2517,11 +2517,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2548,10 +2543,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128794496</v>
+        <v>128794491</v>
       </c>
       <c r="B21" t="n">
-        <v>80222</v>
+        <v>57716</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2559,21 +2554,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2583,10 +2578,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511485</v>
+        <v>510658</v>
       </c>
       <c r="R21" t="n">
-        <v>7106629</v>
+        <v>7106454</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2619,6 +2614,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2648,7 +2648,7 @@
         <v>128794498</v>
       </c>
       <c r="B22" t="n">
-        <v>91790</v>
+        <v>91795</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         <v>128794476</v>
       </c>
       <c r="B23" t="n">
-        <v>91852</v>
+        <v>91857</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2840,10 +2840,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128794525</v>
+        <v>128794517</v>
       </c>
       <c r="B24" t="n">
-        <v>88894</v>
+        <v>79120</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2851,21 +2851,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2875,10 +2875,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>510696</v>
+        <v>511489</v>
       </c>
       <c r="R24" t="n">
-        <v>7106461</v>
+        <v>7106495</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2911,6 +2911,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2937,10 +2942,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128794515</v>
+        <v>128794525</v>
       </c>
       <c r="B25" t="n">
-        <v>91512</v>
+        <v>88899</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2948,21 +2953,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2972,10 +2977,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>511143</v>
+        <v>510696</v>
       </c>
       <c r="R25" t="n">
-        <v>7106625</v>
+        <v>7106461</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3034,10 +3039,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128794517</v>
+        <v>128794515</v>
       </c>
       <c r="B26" t="n">
-        <v>79116</v>
+        <v>91517</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3045,21 +3050,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3069,10 +3074,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>511489</v>
+        <v>511143</v>
       </c>
       <c r="R26" t="n">
-        <v>7106495</v>
+        <v>7106625</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3105,11 +3110,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3139,7 +3139,7 @@
         <v>128794486</v>
       </c>
       <c r="B27" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>128794511</v>
       </c>
       <c r="B28" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>128794503</v>
       </c>
       <c r="B29" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>128794516</v>
       </c>
       <c r="B30" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3529,32 +3529,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128794497</v>
+        <v>128794502</v>
       </c>
       <c r="B31" t="n">
-        <v>91948</v>
+        <v>80225</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3564,10 +3564,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>510812</v>
+        <v>510867</v>
       </c>
       <c r="R31" t="n">
-        <v>7106615</v>
+        <v>7106619</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3626,32 +3626,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128794502</v>
+        <v>128794497</v>
       </c>
       <c r="B32" t="n">
-        <v>80221</v>
+        <v>91953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3661,10 +3661,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>510867</v>
+        <v>510812</v>
       </c>
       <c r="R32" t="n">
-        <v>7106619</v>
+        <v>7106615</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3726,7 +3726,7 @@
         <v>128794505</v>
       </c>
       <c r="B33" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>128794521</v>
       </c>
       <c r="B34" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>128794504</v>
       </c>
       <c r="B35" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         <v>128794500</v>
       </c>
       <c r="B38" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4328,10 +4328,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128794513</v>
+        <v>128794523</v>
       </c>
       <c r="B39" t="n">
-        <v>91512</v>
+        <v>79120</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4339,21 +4339,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4363,10 +4363,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>511247</v>
+        <v>510685</v>
       </c>
       <c r="R39" t="n">
-        <v>7106612</v>
+        <v>7106500</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4425,10 +4425,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128794523</v>
+        <v>128794513</v>
       </c>
       <c r="B40" t="n">
-        <v>79116</v>
+        <v>91517</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4436,21 +4436,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4460,10 +4460,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>510685</v>
+        <v>511247</v>
       </c>
       <c r="R40" t="n">
-        <v>7106500</v>
+        <v>7106612</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4525,7 +4525,7 @@
         <v>128794484</v>
       </c>
       <c r="B41" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>128794510</v>
       </c>
       <c r="B42" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>128794512</v>
       </c>
       <c r="B43" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>128794526</v>
       </c>
       <c r="B44" t="n">
-        <v>89472</v>
+        <v>89477</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 31817-2025 artfynd.xlsx
+++ b/artfynd/A 31817-2025 artfynd.xlsx
@@ -2446,10 +2446,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128794496</v>
+        <v>128794491</v>
       </c>
       <c r="B20" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2457,21 +2457,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511485</v>
+        <v>510658</v>
       </c>
       <c r="R20" t="n">
-        <v>7106629</v>
+        <v>7106454</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2517,6 +2517,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2543,10 +2548,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128794491</v>
+        <v>128794496</v>
       </c>
       <c r="B21" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2554,21 +2559,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2578,10 +2583,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>510658</v>
+        <v>511485</v>
       </c>
       <c r="R21" t="n">
-        <v>7106454</v>
+        <v>7106629</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2614,11 +2619,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 31817-2025 artfynd.xlsx
+++ b/artfynd/A 31817-2025 artfynd.xlsx
@@ -874,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128794477</v>
+        <v>128794519</v>
       </c>
       <c r="B4" t="n">
-        <v>91879</v>
+        <v>79034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510687</v>
+        <v>511436</v>
       </c>
       <c r="R4" t="n">
-        <v>7106478</v>
+        <v>7106614</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,7 +976,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128794519</v>
+        <v>128794520</v>
       </c>
       <c r="B5" t="n">
         <v>79034</v>
@@ -1006,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511436</v>
+        <v>511309</v>
       </c>
       <c r="R5" t="n">
-        <v>7106614</v>
+        <v>7106636</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1042,11 +1047,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,32 +1073,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128794520</v>
+        <v>128794477</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>91882</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511309</v>
+        <v>510687</v>
       </c>
       <c r="R6" t="n">
-        <v>7106636</v>
+        <v>7106478</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128794499</v>
+        <v>128794492</v>
       </c>
       <c r="B7" t="n">
-        <v>80139</v>
+        <v>57723</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511149</v>
+        <v>510773</v>
       </c>
       <c r="R7" t="n">
-        <v>7106300</v>
+        <v>7106391</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1241,6 +1241,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,10 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128794492</v>
+        <v>128794499</v>
       </c>
       <c r="B8" t="n">
-        <v>57723</v>
+        <v>80139</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1283,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510773</v>
+        <v>511149</v>
       </c>
       <c r="R8" t="n">
-        <v>7106391</v>
+        <v>7106300</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1338,11 +1343,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1372,7 +1372,7 @@
         <v>128794485</v>
       </c>
       <c r="B9" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>128794479</v>
       </c>
       <c r="B10" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>128794480</v>
       </c>
       <c r="B11" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1660,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128794509</v>
+        <v>128794482</v>
       </c>
       <c r="B12" t="n">
-        <v>91516</v>
+        <v>91523</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1671,21 +1671,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>510663</v>
+        <v>510816</v>
       </c>
       <c r="R12" t="n">
-        <v>7106445</v>
+        <v>7106613</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128794482</v>
+        <v>128794481</v>
       </c>
       <c r="B13" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510816</v>
+        <v>510842</v>
       </c>
       <c r="R13" t="n">
-        <v>7106613</v>
+        <v>7106609</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128794481</v>
+        <v>128794478</v>
       </c>
       <c r="B14" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>510842</v>
+        <v>511159</v>
       </c>
       <c r="R14" t="n">
-        <v>7106609</v>
+        <v>7106615</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128794478</v>
+        <v>128794509</v>
       </c>
       <c r="B15" t="n">
-        <v>91520</v>
+        <v>91519</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1962,21 +1962,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>511159</v>
+        <v>510663</v>
       </c>
       <c r="R15" t="n">
-        <v>7106615</v>
+        <v>7106445</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2242,10 +2242,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128794488</v>
+        <v>128794524</v>
       </c>
       <c r="B18" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2253,21 +2253,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>510695</v>
+        <v>510700</v>
       </c>
       <c r="R18" t="n">
-        <v>7106401</v>
+        <v>7106468</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Granska rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2344,10 +2344,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128794524</v>
+        <v>128794488</v>
       </c>
       <c r="B19" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2355,21 +2355,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>510700</v>
+        <v>510695</v>
       </c>
       <c r="R19" t="n">
-        <v>7106468</v>
+        <v>7106401</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2419,7 +2419,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Granska rikligt</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2446,10 +2446,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128794491</v>
+        <v>128794496</v>
       </c>
       <c r="B20" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2457,21 +2457,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>510658</v>
+        <v>511485</v>
       </c>
       <c r="R20" t="n">
-        <v>7106454</v>
+        <v>7106629</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2517,11 +2517,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2548,10 +2543,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128794496</v>
+        <v>128794491</v>
       </c>
       <c r="B21" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2559,21 +2554,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2583,10 +2578,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511485</v>
+        <v>510658</v>
       </c>
       <c r="R21" t="n">
-        <v>7106629</v>
+        <v>7106454</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2619,6 +2614,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2648,7 +2648,7 @@
         <v>128794498</v>
       </c>
       <c r="B22" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         <v>128794476</v>
       </c>
       <c r="B23" t="n">
-        <v>91879</v>
+        <v>91882</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2840,10 +2840,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128794515</v>
+        <v>128794517</v>
       </c>
       <c r="B24" t="n">
-        <v>91538</v>
+        <v>79034</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2851,21 +2851,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2875,10 +2875,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>511143</v>
+        <v>511489</v>
       </c>
       <c r="R24" t="n">
-        <v>7106625</v>
+        <v>7106495</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2911,6 +2911,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2937,10 +2942,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128794517</v>
+        <v>128794525</v>
       </c>
       <c r="B25" t="n">
-        <v>79034</v>
+        <v>88923</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2948,21 +2953,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2972,10 +2977,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>511489</v>
+        <v>510696</v>
       </c>
       <c r="R25" t="n">
-        <v>7106495</v>
+        <v>7106461</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3008,11 +3013,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3039,10 +3039,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128794525</v>
+        <v>128794515</v>
       </c>
       <c r="B26" t="n">
-        <v>88920</v>
+        <v>91541</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3050,21 +3050,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>510696</v>
+        <v>511143</v>
       </c>
       <c r="R26" t="n">
-        <v>7106461</v>
+        <v>7106625</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3139,7 +3139,7 @@
         <v>128794486</v>
       </c>
       <c r="B27" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3233,10 +3233,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128794503</v>
+        <v>128794516</v>
       </c>
       <c r="B28" t="n">
-        <v>80139</v>
+        <v>79034</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3244,21 +3244,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>510694</v>
+        <v>511210</v>
       </c>
       <c r="R28" t="n">
-        <v>7106493</v>
+        <v>7106268</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3304,6 +3304,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3333,7 +3338,7 @@
         <v>128794511</v>
       </c>
       <c r="B29" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3427,10 +3432,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128794516</v>
+        <v>128794503</v>
       </c>
       <c r="B30" t="n">
-        <v>79034</v>
+        <v>80139</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3438,21 +3443,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3462,10 +3467,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>511210</v>
+        <v>510694</v>
       </c>
       <c r="R30" t="n">
-        <v>7106268</v>
+        <v>7106493</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3498,11 +3503,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3532,7 +3532,7 @@
         <v>128794497</v>
       </c>
       <c r="B31" t="n">
-        <v>91975</v>
+        <v>91978</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3723,10 +3723,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128794505</v>
+        <v>128794521</v>
       </c>
       <c r="B33" t="n">
-        <v>80139</v>
+        <v>79034</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3734,21 +3734,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>510689</v>
+        <v>511134</v>
       </c>
       <c r="R33" t="n">
-        <v>7106463</v>
+        <v>7106628</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3794,6 +3794,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3820,10 +3825,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128794521</v>
+        <v>128794505</v>
       </c>
       <c r="B34" t="n">
-        <v>79034</v>
+        <v>80139</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3831,21 +3836,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3855,10 +3860,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>511134</v>
+        <v>510689</v>
       </c>
       <c r="R34" t="n">
-        <v>7106628</v>
+        <v>7106463</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3891,11 +3896,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3922,10 +3922,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128794504</v>
+        <v>128794489</v>
       </c>
       <c r="B35" t="n">
-        <v>80139</v>
+        <v>57723</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3933,21 +3933,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3957,10 +3957,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>510707</v>
+        <v>510914</v>
       </c>
       <c r="R35" t="n">
-        <v>7106493</v>
+        <v>7106330</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3993,6 +3993,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4019,10 +4024,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128794489</v>
+        <v>128794504</v>
       </c>
       <c r="B36" t="n">
-        <v>57723</v>
+        <v>80139</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4030,21 +4035,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4054,10 +4059,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>510914</v>
+        <v>510707</v>
       </c>
       <c r="R36" t="n">
-        <v>7106330</v>
+        <v>7106493</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4090,11 +4095,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4328,10 +4328,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128794513</v>
+        <v>128794523</v>
       </c>
       <c r="B39" t="n">
-        <v>91538</v>
+        <v>79034</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4339,21 +4339,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4363,10 +4363,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>511247</v>
+        <v>510685</v>
       </c>
       <c r="R39" t="n">
-        <v>7106612</v>
+        <v>7106500</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4425,10 +4425,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128794523</v>
+        <v>128794513</v>
       </c>
       <c r="B40" t="n">
-        <v>79034</v>
+        <v>91541</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4436,21 +4436,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4460,10 +4460,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>510685</v>
+        <v>511247</v>
       </c>
       <c r="R40" t="n">
-        <v>7106500</v>
+        <v>7106612</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4522,32 +4522,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128794512</v>
+        <v>128794526</v>
       </c>
       <c r="B41" t="n">
-        <v>91538</v>
+        <v>89501</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>236437</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brun klibbskivling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Limacella glioderma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Maire</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4557,10 +4557,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>511307</v>
+        <v>510763</v>
       </c>
       <c r="R41" t="n">
-        <v>7106634</v>
+        <v>7106387</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4622,7 +4622,7 @@
         <v>128794484</v>
       </c>
       <c r="B42" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>128794510</v>
       </c>
       <c r="B43" t="n">
-        <v>91534</v>
+        <v>91537</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4813,32 +4813,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128794526</v>
+        <v>128794512</v>
       </c>
       <c r="B44" t="n">
-        <v>89498</v>
+        <v>91541</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>236437</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brun klibbskivling</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Limacella glioderma</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Maire</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4848,10 +4848,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>510763</v>
+        <v>511307</v>
       </c>
       <c r="R44" t="n">
-        <v>7106387</v>
+        <v>7106634</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 31817-2025 artfynd.xlsx
+++ b/artfynd/A 31817-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128794507</v>
       </c>
       <c r="B2" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128794508</v>
       </c>
       <c r="B3" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128794519</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128794520</v>
+        <v>128794492</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511309</v>
+        <v>510773</v>
       </c>
       <c r="R5" t="n">
-        <v>7106636</v>
+        <v>7106391</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,6 +1047,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,7 +1081,7 @@
         <v>128794477</v>
       </c>
       <c r="B6" t="n">
-        <v>91882</v>
+        <v>91885</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1170,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128794492</v>
+        <v>128794499</v>
       </c>
       <c r="B7" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1186,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510773</v>
+        <v>511149</v>
       </c>
       <c r="R7" t="n">
-        <v>7106391</v>
+        <v>7106300</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1241,11 +1246,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1272,10 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128794499</v>
+        <v>128794520</v>
       </c>
       <c r="B8" t="n">
-        <v>80139</v>
+        <v>79035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,21 +1283,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511149</v>
+        <v>511309</v>
       </c>
       <c r="R8" t="n">
-        <v>7106300</v>
+        <v>7106636</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,7 +1372,7 @@
         <v>128794485</v>
       </c>
       <c r="B9" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>128794479</v>
       </c>
       <c r="B10" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>128794480</v>
       </c>
       <c r="B11" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1660,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128794482</v>
+        <v>128794501</v>
       </c>
       <c r="B12" t="n">
-        <v>91523</v>
+        <v>80140</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1671,21 +1671,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>510816</v>
+        <v>511349</v>
       </c>
       <c r="R12" t="n">
-        <v>7106613</v>
+        <v>7106644</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128794481</v>
+        <v>128794506</v>
       </c>
       <c r="B13" t="n">
-        <v>91523</v>
+        <v>80140</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510842</v>
+        <v>510758</v>
       </c>
       <c r="R13" t="n">
-        <v>7106609</v>
+        <v>7106421</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128794478</v>
+        <v>128794509</v>
       </c>
       <c r="B14" t="n">
-        <v>91523</v>
+        <v>91522</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511159</v>
+        <v>510663</v>
       </c>
       <c r="R14" t="n">
-        <v>7106615</v>
+        <v>7106445</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128794509</v>
+        <v>128794482</v>
       </c>
       <c r="B15" t="n">
-        <v>91519</v>
+        <v>91526</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1962,21 +1962,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>510663</v>
+        <v>510816</v>
       </c>
       <c r="R15" t="n">
-        <v>7106445</v>
+        <v>7106613</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128794501</v>
+        <v>128794481</v>
       </c>
       <c r="B16" t="n">
-        <v>80139</v>
+        <v>91526</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,21 +2059,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511349</v>
+        <v>510842</v>
       </c>
       <c r="R16" t="n">
-        <v>7106644</v>
+        <v>7106609</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,10 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128794506</v>
+        <v>128794478</v>
       </c>
       <c r="B17" t="n">
-        <v>80139</v>
+        <v>91526</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,21 +2156,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>510758</v>
+        <v>511159</v>
       </c>
       <c r="R17" t="n">
-        <v>7106421</v>
+        <v>7106615</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2242,10 +2242,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128794524</v>
+        <v>128794488</v>
       </c>
       <c r="B18" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2253,21 +2253,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>510700</v>
+        <v>510695</v>
       </c>
       <c r="R18" t="n">
-        <v>7106468</v>
+        <v>7106401</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Granska rikligt</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2344,10 +2344,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128794488</v>
+        <v>128794524</v>
       </c>
       <c r="B19" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2355,21 +2355,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>510695</v>
+        <v>510700</v>
       </c>
       <c r="R19" t="n">
-        <v>7106401</v>
+        <v>7106468</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2419,7 +2419,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Granska rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2449,7 +2449,7 @@
         <v>128794496</v>
       </c>
       <c r="B20" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         <v>128794498</v>
       </c>
       <c r="B22" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         <v>128794476</v>
       </c>
       <c r="B23" t="n">
-        <v>91882</v>
+        <v>91885</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2840,10 +2840,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128794517</v>
+        <v>128794525</v>
       </c>
       <c r="B24" t="n">
-        <v>79034</v>
+        <v>88926</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2851,21 +2851,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2875,10 +2875,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>511489</v>
+        <v>510696</v>
       </c>
       <c r="R24" t="n">
-        <v>7106495</v>
+        <v>7106461</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2911,11 +2911,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2942,10 +2937,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128794525</v>
+        <v>128794515</v>
       </c>
       <c r="B25" t="n">
-        <v>88923</v>
+        <v>91544</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2953,21 +2948,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2977,10 +2972,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>510696</v>
+        <v>511143</v>
       </c>
       <c r="R25" t="n">
-        <v>7106461</v>
+        <v>7106625</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3039,10 +3034,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128794515</v>
+        <v>128794517</v>
       </c>
       <c r="B26" t="n">
-        <v>91541</v>
+        <v>79035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3050,21 +3045,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3074,10 +3069,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>511143</v>
+        <v>511489</v>
       </c>
       <c r="R26" t="n">
-        <v>7106625</v>
+        <v>7106495</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3110,6 +3105,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3136,10 +3136,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128794486</v>
+        <v>128794516</v>
       </c>
       <c r="B27" t="n">
-        <v>91523</v>
+        <v>79035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3147,21 +3147,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>510777</v>
+        <v>511210</v>
       </c>
       <c r="R27" t="n">
-        <v>7106379</v>
+        <v>7106268</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3207,6 +3207,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3233,10 +3238,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128794516</v>
+        <v>128794503</v>
       </c>
       <c r="B28" t="n">
-        <v>79034</v>
+        <v>80140</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3244,21 +3249,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3268,10 +3273,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>511210</v>
+        <v>510694</v>
       </c>
       <c r="R28" t="n">
-        <v>7106268</v>
+        <v>7106493</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3304,11 +3309,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3335,10 +3335,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128794511</v>
+        <v>128794486</v>
       </c>
       <c r="B29" t="n">
-        <v>91541</v>
+        <v>91526</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3346,21 +3346,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>511450</v>
+        <v>510777</v>
       </c>
       <c r="R29" t="n">
-        <v>7106469</v>
+        <v>7106379</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3432,10 +3432,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128794503</v>
+        <v>128794511</v>
       </c>
       <c r="B30" t="n">
-        <v>80139</v>
+        <v>91544</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3443,21 +3443,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>510694</v>
+        <v>511450</v>
       </c>
       <c r="R30" t="n">
-        <v>7106493</v>
+        <v>7106469</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3532,7 +3532,7 @@
         <v>128794497</v>
       </c>
       <c r="B31" t="n">
-        <v>91978</v>
+        <v>91981</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>128794502</v>
       </c>
       <c r="B32" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         <v>128794521</v>
       </c>
       <c r="B33" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>128794505</v>
       </c>
       <c r="B34" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3922,10 +3922,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128794489</v>
+        <v>128794504</v>
       </c>
       <c r="B35" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3933,21 +3933,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3957,10 +3957,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>510914</v>
+        <v>510707</v>
       </c>
       <c r="R35" t="n">
-        <v>7106330</v>
+        <v>7106493</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3993,11 +3993,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4024,10 +4019,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128794504</v>
+        <v>128794489</v>
       </c>
       <c r="B36" t="n">
-        <v>80139</v>
+        <v>57723</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4035,21 +4030,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4059,10 +4054,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>510707</v>
+        <v>510914</v>
       </c>
       <c r="R36" t="n">
-        <v>7106493</v>
+        <v>7106330</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4095,6 +4090,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4234,7 +4234,7 @@
         <v>128794500</v>
       </c>
       <c r="B38" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>128794523</v>
       </c>
       <c r="B39" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>128794513</v>
       </c>
       <c r="B40" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4522,32 +4522,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128794526</v>
+        <v>128794512</v>
       </c>
       <c r="B41" t="n">
-        <v>89501</v>
+        <v>91544</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>236437</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Brun klibbskivling</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Limacella glioderma</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Maire</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4557,10 +4557,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>510763</v>
+        <v>511307</v>
       </c>
       <c r="R41" t="n">
-        <v>7106387</v>
+        <v>7106634</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4622,7 +4622,7 @@
         <v>128794484</v>
       </c>
       <c r="B42" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>128794510</v>
       </c>
       <c r="B43" t="n">
-        <v>91537</v>
+        <v>91540</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4813,32 +4813,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128794512</v>
+        <v>128794526</v>
       </c>
       <c r="B44" t="n">
-        <v>91541</v>
+        <v>89504</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>236437</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brun klibbskivling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Limacella glioderma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Maire</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4848,10 +4848,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>511307</v>
+        <v>510763</v>
       </c>
       <c r="R44" t="n">
-        <v>7106634</v>
+        <v>7106387</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 31817-2025 artfynd.xlsx
+++ b/artfynd/A 31817-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128794507</v>
+        <v>128794508</v>
       </c>
       <c r="B2" t="n">
         <v>80140</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510771</v>
+        <v>510782</v>
       </c>
       <c r="R2" t="n">
-        <v>7106380</v>
+        <v>7106356</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128794508</v>
+        <v>128794507</v>
       </c>
       <c r="B3" t="n">
         <v>80140</v>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510782</v>
+        <v>510771</v>
       </c>
       <c r="R3" t="n">
-        <v>7106356</v>
+        <v>7106380</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128794519</v>
+        <v>128794477</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>91885</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511436</v>
+        <v>510687</v>
       </c>
       <c r="R4" t="n">
-        <v>7106614</v>
+        <v>7106478</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128794492</v>
+        <v>128794519</v>
       </c>
       <c r="B5" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>510773</v>
+        <v>511436</v>
       </c>
       <c r="R5" t="n">
-        <v>7106391</v>
+        <v>7106614</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,7 +1046,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,32 +1073,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128794477</v>
+        <v>128794492</v>
       </c>
       <c r="B6" t="n">
-        <v>91885</v>
+        <v>57723</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510687</v>
+        <v>510773</v>
       </c>
       <c r="R6" t="n">
-        <v>7106478</v>
+        <v>7106391</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,6 +1144,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128794499</v>
+        <v>128794520</v>
       </c>
       <c r="B7" t="n">
-        <v>80140</v>
+        <v>79035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,21 +1186,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511149</v>
+        <v>511309</v>
       </c>
       <c r="R7" t="n">
-        <v>7106300</v>
+        <v>7106636</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1272,10 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128794520</v>
+        <v>128794499</v>
       </c>
       <c r="B8" t="n">
-        <v>79035</v>
+        <v>80140</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,21 +1283,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511309</v>
+        <v>511149</v>
       </c>
       <c r="R8" t="n">
-        <v>7106636</v>
+        <v>7106300</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1660,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128794501</v>
+        <v>128794482</v>
       </c>
       <c r="B12" t="n">
-        <v>80140</v>
+        <v>91526</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1671,21 +1671,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511349</v>
+        <v>510816</v>
       </c>
       <c r="R12" t="n">
-        <v>7106644</v>
+        <v>7106613</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128794506</v>
+        <v>128794481</v>
       </c>
       <c r="B13" t="n">
-        <v>80140</v>
+        <v>91526</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510758</v>
+        <v>510842</v>
       </c>
       <c r="R13" t="n">
-        <v>7106421</v>
+        <v>7106609</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128794509</v>
+        <v>128794478</v>
       </c>
       <c r="B14" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>510663</v>
+        <v>511159</v>
       </c>
       <c r="R14" t="n">
-        <v>7106445</v>
+        <v>7106615</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128794482</v>
+        <v>128794509</v>
       </c>
       <c r="B15" t="n">
-        <v>91526</v>
+        <v>91522</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1962,21 +1962,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>510816</v>
+        <v>510663</v>
       </c>
       <c r="R15" t="n">
-        <v>7106613</v>
+        <v>7106445</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128794481</v>
+        <v>128794501</v>
       </c>
       <c r="B16" t="n">
-        <v>91526</v>
+        <v>80140</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,21 +2059,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>510842</v>
+        <v>511349</v>
       </c>
       <c r="R16" t="n">
-        <v>7106609</v>
+        <v>7106644</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,10 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128794478</v>
+        <v>128794506</v>
       </c>
       <c r="B17" t="n">
-        <v>91526</v>
+        <v>80140</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,21 +2156,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511159</v>
+        <v>510758</v>
       </c>
       <c r="R17" t="n">
-        <v>7106615</v>
+        <v>7106421</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128794516</v>
+        <v>128794511</v>
       </c>
       <c r="B27" t="n">
-        <v>79035</v>
+        <v>91544</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3147,21 +3147,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>511210</v>
+        <v>511450</v>
       </c>
       <c r="R27" t="n">
-        <v>7106268</v>
+        <v>7106469</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3207,11 +3207,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3238,10 +3233,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128794503</v>
+        <v>128794516</v>
       </c>
       <c r="B28" t="n">
-        <v>80140</v>
+        <v>79035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3249,21 +3244,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3273,10 +3268,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>510694</v>
+        <v>511210</v>
       </c>
       <c r="R28" t="n">
-        <v>7106493</v>
+        <v>7106268</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3309,6 +3304,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3335,10 +3335,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128794486</v>
+        <v>128794503</v>
       </c>
       <c r="B29" t="n">
-        <v>91526</v>
+        <v>80140</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3346,21 +3346,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>510777</v>
+        <v>510694</v>
       </c>
       <c r="R29" t="n">
-        <v>7106379</v>
+        <v>7106493</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3432,10 +3432,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128794511</v>
+        <v>128794486</v>
       </c>
       <c r="B30" t="n">
-        <v>91544</v>
+        <v>91526</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3443,21 +3443,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>511450</v>
+        <v>510777</v>
       </c>
       <c r="R30" t="n">
-        <v>7106469</v>
+        <v>7106379</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4328,10 +4328,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128794523</v>
+        <v>128794513</v>
       </c>
       <c r="B39" t="n">
-        <v>79035</v>
+        <v>91544</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4339,21 +4339,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4363,10 +4363,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>510685</v>
+        <v>511247</v>
       </c>
       <c r="R39" t="n">
-        <v>7106500</v>
+        <v>7106612</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4425,10 +4425,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128794513</v>
+        <v>128794523</v>
       </c>
       <c r="B40" t="n">
-        <v>91544</v>
+        <v>79035</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4436,21 +4436,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4460,10 +4460,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>511247</v>
+        <v>510685</v>
       </c>
       <c r="R40" t="n">
-        <v>7106612</v>
+        <v>7106500</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4522,10 +4522,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128794512</v>
+        <v>128794484</v>
       </c>
       <c r="B41" t="n">
-        <v>91544</v>
+        <v>91526</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4533,21 +4533,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4557,10 +4557,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>511307</v>
+        <v>510684</v>
       </c>
       <c r="R41" t="n">
-        <v>7106634</v>
+        <v>7106476</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4619,10 +4619,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128794484</v>
+        <v>128794510</v>
       </c>
       <c r="B42" t="n">
-        <v>91526</v>
+        <v>91540</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4630,21 +4630,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4654,10 +4654,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>510684</v>
+        <v>510841</v>
       </c>
       <c r="R42" t="n">
-        <v>7106476</v>
+        <v>7106597</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4716,10 +4716,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128794510</v>
+        <v>128794512</v>
       </c>
       <c r="B43" t="n">
-        <v>91540</v>
+        <v>91544</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4727,21 +4727,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4751,10 +4751,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>510841</v>
+        <v>511307</v>
       </c>
       <c r="R43" t="n">
-        <v>7106597</v>
+        <v>7106634</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 31817-2025 artfynd.xlsx
+++ b/artfynd/A 31817-2025 artfynd.xlsx
@@ -1660,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128794482</v>
+        <v>128794509</v>
       </c>
       <c r="B12" t="n">
-        <v>91526</v>
+        <v>91522</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1671,21 +1671,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>510816</v>
+        <v>510663</v>
       </c>
       <c r="R12" t="n">
-        <v>7106613</v>
+        <v>7106445</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128794481</v>
+        <v>128794501</v>
       </c>
       <c r="B13" t="n">
-        <v>91526</v>
+        <v>80140</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510842</v>
+        <v>511349</v>
       </c>
       <c r="R13" t="n">
-        <v>7106609</v>
+        <v>7106644</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1854,7 +1854,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128794478</v>
+        <v>128794482</v>
       </c>
       <c r="B14" t="n">
         <v>91526</v>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511159</v>
+        <v>510816</v>
       </c>
       <c r="R14" t="n">
-        <v>7106615</v>
+        <v>7106613</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128794509</v>
+        <v>128794481</v>
       </c>
       <c r="B15" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1962,21 +1962,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>510663</v>
+        <v>510842</v>
       </c>
       <c r="R15" t="n">
-        <v>7106445</v>
+        <v>7106609</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128794501</v>
+        <v>128794478</v>
       </c>
       <c r="B16" t="n">
-        <v>80140</v>
+        <v>91526</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,21 +2059,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511349</v>
+        <v>511159</v>
       </c>
       <c r="R16" t="n">
-        <v>7106644</v>
+        <v>7106615</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -3529,32 +3529,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128794497</v>
+        <v>128794502</v>
       </c>
       <c r="B31" t="n">
-        <v>91981</v>
+        <v>80140</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3564,10 +3564,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>510812</v>
+        <v>510867</v>
       </c>
       <c r="R31" t="n">
-        <v>7106615</v>
+        <v>7106619</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3626,32 +3626,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128794502</v>
+        <v>128794497</v>
       </c>
       <c r="B32" t="n">
-        <v>80140</v>
+        <v>91981</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3661,10 +3661,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>510867</v>
+        <v>510812</v>
       </c>
       <c r="R32" t="n">
-        <v>7106619</v>
+        <v>7106615</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4522,32 +4522,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128794484</v>
+        <v>128794526</v>
       </c>
       <c r="B41" t="n">
-        <v>91526</v>
+        <v>89504</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>236437</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brun klibbskivling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Limacella glioderma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Maire</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4557,10 +4557,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>510684</v>
+        <v>510763</v>
       </c>
       <c r="R41" t="n">
-        <v>7106476</v>
+        <v>7106387</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4619,10 +4619,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128794510</v>
+        <v>128794484</v>
       </c>
       <c r="B42" t="n">
-        <v>91540</v>
+        <v>91526</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4630,21 +4630,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4654,10 +4654,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>510841</v>
+        <v>510684</v>
       </c>
       <c r="R42" t="n">
-        <v>7106597</v>
+        <v>7106476</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4716,10 +4716,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128794512</v>
+        <v>128794510</v>
       </c>
       <c r="B43" t="n">
-        <v>91544</v>
+        <v>91540</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4727,21 +4727,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4751,10 +4751,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>511307</v>
+        <v>510841</v>
       </c>
       <c r="R43" t="n">
-        <v>7106634</v>
+        <v>7106597</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4813,32 +4813,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128794526</v>
+        <v>128794512</v>
       </c>
       <c r="B44" t="n">
-        <v>89504</v>
+        <v>91544</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>236437</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brun klibbskivling</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Limacella glioderma</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Maire</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4848,10 +4848,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>510763</v>
+        <v>511307</v>
       </c>
       <c r="R44" t="n">
-        <v>7106387</v>
+        <v>7106634</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 31817-2025 artfynd.xlsx
+++ b/artfynd/A 31817-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128794508</v>
+        <v>128794507</v>
       </c>
       <c r="B2" t="n">
         <v>80140</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510782</v>
+        <v>510771</v>
       </c>
       <c r="R2" t="n">
-        <v>7106356</v>
+        <v>7106380</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128794507</v>
+        <v>128794508</v>
       </c>
       <c r="B3" t="n">
         <v>80140</v>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510771</v>
+        <v>510782</v>
       </c>
       <c r="R3" t="n">
-        <v>7106380</v>
+        <v>7106356</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128794477</v>
+        <v>128794492</v>
       </c>
       <c r="B4" t="n">
-        <v>91885</v>
+        <v>57723</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510687</v>
+        <v>510773</v>
       </c>
       <c r="R4" t="n">
-        <v>7106478</v>
+        <v>7106391</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1073,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128794492</v>
+        <v>128794520</v>
       </c>
       <c r="B6" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510773</v>
+        <v>511309</v>
       </c>
       <c r="R6" t="n">
-        <v>7106391</v>
+        <v>7106636</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,11 +1149,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,32 +1175,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128794520</v>
+        <v>128794477</v>
       </c>
       <c r="B7" t="n">
-        <v>79035</v>
+        <v>91885</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511309</v>
+        <v>510687</v>
       </c>
       <c r="R7" t="n">
-        <v>7106636</v>
+        <v>7106478</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128794501</v>
+        <v>128794482</v>
       </c>
       <c r="B13" t="n">
-        <v>80140</v>
+        <v>91526</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511349</v>
+        <v>510816</v>
       </c>
       <c r="R13" t="n">
-        <v>7106644</v>
+        <v>7106613</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1854,7 +1854,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128794482</v>
+        <v>128794481</v>
       </c>
       <c r="B14" t="n">
         <v>91526</v>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>510816</v>
+        <v>510842</v>
       </c>
       <c r="R14" t="n">
-        <v>7106613</v>
+        <v>7106609</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1951,7 +1951,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128794481</v>
+        <v>128794478</v>
       </c>
       <c r="B15" t="n">
         <v>91526</v>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>510842</v>
+        <v>511159</v>
       </c>
       <c r="R15" t="n">
-        <v>7106609</v>
+        <v>7106615</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128794478</v>
+        <v>128794501</v>
       </c>
       <c r="B16" t="n">
-        <v>91526</v>
+        <v>80140</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,21 +2059,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511159</v>
+        <v>511349</v>
       </c>
       <c r="R16" t="n">
-        <v>7106615</v>
+        <v>7106644</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128794515</v>
+        <v>128794517</v>
       </c>
       <c r="B25" t="n">
-        <v>91544</v>
+        <v>79035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2948,21 +2948,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>511143</v>
+        <v>511489</v>
       </c>
       <c r="R25" t="n">
-        <v>7106625</v>
+        <v>7106495</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3008,6 +3008,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3034,10 +3039,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128794517</v>
+        <v>128794515</v>
       </c>
       <c r="B26" t="n">
-        <v>79035</v>
+        <v>91544</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3045,21 +3050,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3069,10 +3074,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>511489</v>
+        <v>511143</v>
       </c>
       <c r="R26" t="n">
-        <v>7106495</v>
+        <v>7106625</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3105,11 +3110,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3136,10 +3136,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128794511</v>
+        <v>128794486</v>
       </c>
       <c r="B27" t="n">
-        <v>91544</v>
+        <v>91526</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3147,21 +3147,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>511450</v>
+        <v>510777</v>
       </c>
       <c r="R27" t="n">
-        <v>7106469</v>
+        <v>7106379</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3335,10 +3335,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128794503</v>
+        <v>128794511</v>
       </c>
       <c r="B29" t="n">
-        <v>80140</v>
+        <v>91544</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3346,21 +3346,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>510694</v>
+        <v>511450</v>
       </c>
       <c r="R29" t="n">
-        <v>7106493</v>
+        <v>7106469</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3432,10 +3432,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128794486</v>
+        <v>128794503</v>
       </c>
       <c r="B30" t="n">
-        <v>91526</v>
+        <v>80140</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3443,21 +3443,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>510777</v>
+        <v>510694</v>
       </c>
       <c r="R30" t="n">
-        <v>7106379</v>
+        <v>7106493</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3529,32 +3529,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128794502</v>
+        <v>128794497</v>
       </c>
       <c r="B31" t="n">
-        <v>80140</v>
+        <v>91981</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3564,10 +3564,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>510867</v>
+        <v>510812</v>
       </c>
       <c r="R31" t="n">
-        <v>7106619</v>
+        <v>7106615</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3626,32 +3626,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128794497</v>
+        <v>128794502</v>
       </c>
       <c r="B32" t="n">
-        <v>91981</v>
+        <v>80140</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3661,10 +3661,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>510812</v>
+        <v>510867</v>
       </c>
       <c r="R32" t="n">
-        <v>7106615</v>
+        <v>7106619</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4522,32 +4522,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128794526</v>
+        <v>128794510</v>
       </c>
       <c r="B41" t="n">
-        <v>89504</v>
+        <v>91540</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>236437</v>
+        <v>1204</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Brun klibbskivling</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Limacella glioderma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Maire</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4557,10 +4557,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>510763</v>
+        <v>510841</v>
       </c>
       <c r="R41" t="n">
-        <v>7106387</v>
+        <v>7106597</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4716,10 +4716,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128794510</v>
+        <v>128794512</v>
       </c>
       <c r="B43" t="n">
-        <v>91540</v>
+        <v>91544</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4727,21 +4727,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4751,10 +4751,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>510841</v>
+        <v>511307</v>
       </c>
       <c r="R43" t="n">
-        <v>7106597</v>
+        <v>7106634</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4813,32 +4813,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128794512</v>
+        <v>128794526</v>
       </c>
       <c r="B44" t="n">
-        <v>91544</v>
+        <v>89504</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>236437</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brun klibbskivling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Limacella glioderma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Maire</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4848,10 +4848,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>511307</v>
+        <v>510763</v>
       </c>
       <c r="R44" t="n">
-        <v>7106634</v>
+        <v>7106387</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 31817-2025 artfynd.xlsx
+++ b/artfynd/A 31817-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128794507</v>
       </c>
       <c r="B2" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128794508</v>
       </c>
       <c r="B3" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128794492</v>
+        <v>128794519</v>
       </c>
       <c r="B4" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510773</v>
+        <v>511436</v>
       </c>
       <c r="R4" t="n">
-        <v>7106391</v>
+        <v>7106614</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,7 +949,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128794519</v>
+        <v>128794499</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>80144</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511436</v>
+        <v>511149</v>
       </c>
       <c r="R5" t="n">
-        <v>7106614</v>
+        <v>7106300</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,11 +1047,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,7 +1076,7 @@
         <v>128794520</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1173,7 @@
         <v>128794477</v>
       </c>
       <c r="B7" t="n">
-        <v>91885</v>
+        <v>91892</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128794499</v>
+        <v>128794492</v>
       </c>
       <c r="B8" t="n">
-        <v>80140</v>
+        <v>57725</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511149</v>
+        <v>510773</v>
       </c>
       <c r="R8" t="n">
-        <v>7106300</v>
+        <v>7106391</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1343,6 +1338,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1372,7 +1372,7 @@
         <v>128794485</v>
       </c>
       <c r="B9" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>128794479</v>
       </c>
       <c r="B10" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>128794480</v>
       </c>
       <c r="B11" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>128794509</v>
       </c>
       <c r="B12" t="n">
-        <v>91522</v>
+        <v>91529</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>128794482</v>
       </c>
       <c r="B13" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>128794481</v>
       </c>
       <c r="B14" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>128794478</v>
       </c>
       <c r="B15" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>128794501</v>
       </c>
       <c r="B16" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>128794506</v>
       </c>
       <c r="B17" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2242,10 +2242,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128794488</v>
+        <v>128794524</v>
       </c>
       <c r="B18" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2253,21 +2253,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>510695</v>
+        <v>510700</v>
       </c>
       <c r="R18" t="n">
-        <v>7106401</v>
+        <v>7106468</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Granska rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2344,10 +2344,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128794524</v>
+        <v>128794488</v>
       </c>
       <c r="B19" t="n">
-        <v>79035</v>
+        <v>57725</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2355,21 +2355,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>510700</v>
+        <v>510695</v>
       </c>
       <c r="R19" t="n">
-        <v>7106468</v>
+        <v>7106401</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2419,7 +2419,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Granska rikligt</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2446,10 +2446,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128794496</v>
+        <v>128794491</v>
       </c>
       <c r="B20" t="n">
-        <v>80141</v>
+        <v>57725</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2457,21 +2457,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511485</v>
+        <v>510658</v>
       </c>
       <c r="R20" t="n">
-        <v>7106629</v>
+        <v>7106454</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2517,6 +2517,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2543,10 +2548,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128794491</v>
+        <v>128794496</v>
       </c>
       <c r="B21" t="n">
-        <v>57723</v>
+        <v>80145</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2554,21 +2559,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2578,10 +2583,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>510658</v>
+        <v>511485</v>
       </c>
       <c r="R21" t="n">
-        <v>7106454</v>
+        <v>7106629</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2614,11 +2619,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2648,7 +2648,7 @@
         <v>128794498</v>
       </c>
       <c r="B22" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         <v>128794476</v>
       </c>
       <c r="B23" t="n">
-        <v>91885</v>
+        <v>91892</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>128794525</v>
       </c>
       <c r="B24" t="n">
-        <v>88926</v>
+        <v>88930</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128794517</v>
+        <v>128794515</v>
       </c>
       <c r="B25" t="n">
-        <v>79035</v>
+        <v>91551</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2948,21 +2948,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>511489</v>
+        <v>511143</v>
       </c>
       <c r="R25" t="n">
-        <v>7106495</v>
+        <v>7106625</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3008,11 +3008,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3039,10 +3034,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128794515</v>
+        <v>128794517</v>
       </c>
       <c r="B26" t="n">
-        <v>91544</v>
+        <v>79039</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3050,21 +3045,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3074,10 +3069,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>511143</v>
+        <v>511489</v>
       </c>
       <c r="R26" t="n">
-        <v>7106625</v>
+        <v>7106495</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3110,6 +3105,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3139,7 +3139,7 @@
         <v>128794486</v>
       </c>
       <c r="B27" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3233,10 +3233,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128794516</v>
+        <v>128794503</v>
       </c>
       <c r="B28" t="n">
-        <v>79035</v>
+        <v>80144</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3244,21 +3244,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>511210</v>
+        <v>510694</v>
       </c>
       <c r="R28" t="n">
-        <v>7106268</v>
+        <v>7106493</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3304,11 +3304,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3338,7 +3333,7 @@
         <v>128794511</v>
       </c>
       <c r="B29" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3432,10 +3427,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128794503</v>
+        <v>128794516</v>
       </c>
       <c r="B30" t="n">
-        <v>80140</v>
+        <v>79039</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3443,21 +3438,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3467,10 +3462,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>510694</v>
+        <v>511210</v>
       </c>
       <c r="R30" t="n">
-        <v>7106493</v>
+        <v>7106268</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3503,6 +3498,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3532,7 +3532,7 @@
         <v>128794497</v>
       </c>
       <c r="B31" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>128794502</v>
       </c>
       <c r="B32" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         <v>128794521</v>
       </c>
       <c r="B33" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>128794505</v>
       </c>
       <c r="B34" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3922,10 +3922,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128794504</v>
+        <v>128794489</v>
       </c>
       <c r="B35" t="n">
-        <v>80140</v>
+        <v>57725</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3933,21 +3933,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3957,10 +3957,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>510707</v>
+        <v>510914</v>
       </c>
       <c r="R35" t="n">
-        <v>7106493</v>
+        <v>7106330</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3993,6 +3993,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4019,10 +4024,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128794489</v>
+        <v>128794504</v>
       </c>
       <c r="B36" t="n">
-        <v>57723</v>
+        <v>80144</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4030,21 +4035,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4054,10 +4059,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>510914</v>
+        <v>510707</v>
       </c>
       <c r="R36" t="n">
-        <v>7106330</v>
+        <v>7106493</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4090,11 +4095,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4124,7 +4124,7 @@
         <v>128794495</v>
       </c>
       <c r="B37" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         <v>128794500</v>
       </c>
       <c r="B38" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4328,10 +4328,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128794513</v>
+        <v>128794523</v>
       </c>
       <c r="B39" t="n">
-        <v>91544</v>
+        <v>79039</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4339,21 +4339,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4363,10 +4363,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>511247</v>
+        <v>510685</v>
       </c>
       <c r="R39" t="n">
-        <v>7106612</v>
+        <v>7106500</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4425,10 +4425,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128794523</v>
+        <v>128794513</v>
       </c>
       <c r="B40" t="n">
-        <v>79035</v>
+        <v>91551</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4436,21 +4436,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4460,10 +4460,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>510685</v>
+        <v>511247</v>
       </c>
       <c r="R40" t="n">
-        <v>7106500</v>
+        <v>7106612</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4522,10 +4522,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128794510</v>
+        <v>128794512</v>
       </c>
       <c r="B41" t="n">
-        <v>91540</v>
+        <v>91551</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4533,21 +4533,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4557,10 +4557,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>510841</v>
+        <v>511307</v>
       </c>
       <c r="R41" t="n">
-        <v>7106597</v>
+        <v>7106634</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4622,7 +4622,7 @@
         <v>128794484</v>
       </c>
       <c r="B42" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4716,10 +4716,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128794512</v>
+        <v>128794510</v>
       </c>
       <c r="B43" t="n">
-        <v>91544</v>
+        <v>91547</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4727,21 +4727,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4751,10 +4751,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>511307</v>
+        <v>510841</v>
       </c>
       <c r="R43" t="n">
-        <v>7106634</v>
+        <v>7106597</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4816,7 +4816,7 @@
         <v>128794526</v>
       </c>
       <c r="B44" t="n">
-        <v>89504</v>
+        <v>89508</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 31817-2025 artfynd.xlsx
+++ b/artfynd/A 31817-2025 artfynd.xlsx
@@ -874,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128794519</v>
+        <v>128794477</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>91892</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511436</v>
+        <v>510687</v>
       </c>
       <c r="R4" t="n">
-        <v>7106614</v>
+        <v>7106478</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1170,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128794477</v>
+        <v>128794519</v>
       </c>
       <c r="B7" t="n">
-        <v>91892</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510687</v>
+        <v>511436</v>
       </c>
       <c r="R7" t="n">
-        <v>7106478</v>
+        <v>7106614</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1241,6 +1236,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -2840,10 +2840,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128794525</v>
+        <v>128794515</v>
       </c>
       <c r="B24" t="n">
-        <v>88930</v>
+        <v>91551</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2851,21 +2851,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2875,10 +2875,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>510696</v>
+        <v>511143</v>
       </c>
       <c r="R24" t="n">
-        <v>7106461</v>
+        <v>7106625</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128794515</v>
+        <v>128794525</v>
       </c>
       <c r="B25" t="n">
-        <v>91551</v>
+        <v>88930</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2948,21 +2948,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>511143</v>
+        <v>510696</v>
       </c>
       <c r="R25" t="n">
-        <v>7106625</v>
+        <v>7106461</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3529,32 +3529,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128794497</v>
+        <v>128794502</v>
       </c>
       <c r="B31" t="n">
-        <v>91988</v>
+        <v>80144</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3564,10 +3564,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>510812</v>
+        <v>510867</v>
       </c>
       <c r="R31" t="n">
-        <v>7106615</v>
+        <v>7106619</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3626,32 +3626,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128794502</v>
+        <v>128794497</v>
       </c>
       <c r="B32" t="n">
-        <v>80144</v>
+        <v>91988</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3661,10 +3661,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>510867</v>
+        <v>510812</v>
       </c>
       <c r="R32" t="n">
-        <v>7106619</v>
+        <v>7106615</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4328,10 +4328,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128794523</v>
+        <v>128794513</v>
       </c>
       <c r="B39" t="n">
-        <v>79039</v>
+        <v>91551</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4339,21 +4339,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4363,10 +4363,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>510685</v>
+        <v>511247</v>
       </c>
       <c r="R39" t="n">
-        <v>7106500</v>
+        <v>7106612</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4425,10 +4425,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128794513</v>
+        <v>128794523</v>
       </c>
       <c r="B40" t="n">
-        <v>91551</v>
+        <v>79039</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4436,21 +4436,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4460,10 +4460,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>511247</v>
+        <v>510685</v>
       </c>
       <c r="R40" t="n">
-        <v>7106612</v>
+        <v>7106500</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>

--- a/artfynd/A 31817-2025 artfynd.xlsx
+++ b/artfynd/A 31817-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128794507</v>
+        <v>128794508</v>
       </c>
       <c r="B2" t="n">
         <v>80144</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510771</v>
+        <v>510782</v>
       </c>
       <c r="R2" t="n">
-        <v>7106380</v>
+        <v>7106356</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128794508</v>
+        <v>128794507</v>
       </c>
       <c r="B3" t="n">
         <v>80144</v>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510782</v>
+        <v>510771</v>
       </c>
       <c r="R3" t="n">
-        <v>7106356</v>
+        <v>7106380</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128794477</v>
+        <v>128794519</v>
       </c>
       <c r="B4" t="n">
-        <v>91892</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510687</v>
+        <v>511436</v>
       </c>
       <c r="R4" t="n">
-        <v>7106478</v>
+        <v>7106614</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128794499</v>
+        <v>128794520</v>
       </c>
       <c r="B5" t="n">
-        <v>80144</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511149</v>
+        <v>511309</v>
       </c>
       <c r="R5" t="n">
-        <v>7106300</v>
+        <v>7106636</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,32 +1073,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128794520</v>
+        <v>128794477</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>91899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511309</v>
+        <v>510687</v>
       </c>
       <c r="R6" t="n">
-        <v>7106636</v>
+        <v>7106478</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128794519</v>
+        <v>128794499</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>80144</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511436</v>
+        <v>511149</v>
       </c>
       <c r="R7" t="n">
-        <v>7106614</v>
+        <v>7106300</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,11 +1241,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,7 +1372,7 @@
         <v>128794485</v>
       </c>
       <c r="B9" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>128794479</v>
       </c>
       <c r="B10" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>128794480</v>
       </c>
       <c r="B11" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1660,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128794509</v>
+        <v>128794482</v>
       </c>
       <c r="B12" t="n">
-        <v>91529</v>
+        <v>91540</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1671,21 +1671,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>510663</v>
+        <v>510816</v>
       </c>
       <c r="R12" t="n">
-        <v>7106445</v>
+        <v>7106613</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128794482</v>
+        <v>128794481</v>
       </c>
       <c r="B13" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510816</v>
+        <v>510842</v>
       </c>
       <c r="R13" t="n">
-        <v>7106613</v>
+        <v>7106609</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128794481</v>
+        <v>128794478</v>
       </c>
       <c r="B14" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>510842</v>
+        <v>511159</v>
       </c>
       <c r="R14" t="n">
-        <v>7106609</v>
+        <v>7106615</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128794478</v>
+        <v>128794501</v>
       </c>
       <c r="B15" t="n">
-        <v>91533</v>
+        <v>80144</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1962,21 +1962,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>511159</v>
+        <v>511349</v>
       </c>
       <c r="R15" t="n">
-        <v>7106615</v>
+        <v>7106644</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128794501</v>
+        <v>128794509</v>
       </c>
       <c r="B16" t="n">
-        <v>80144</v>
+        <v>91536</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,21 +2059,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511349</v>
+        <v>510663</v>
       </c>
       <c r="R16" t="n">
-        <v>7106644</v>
+        <v>7106445</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2446,10 +2446,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128794491</v>
+        <v>128794496</v>
       </c>
       <c r="B20" t="n">
-        <v>57725</v>
+        <v>80145</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2457,21 +2457,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>510658</v>
+        <v>511485</v>
       </c>
       <c r="R20" t="n">
-        <v>7106454</v>
+        <v>7106629</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2517,11 +2517,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2548,10 +2543,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128794496</v>
+        <v>128794491</v>
       </c>
       <c r="B21" t="n">
-        <v>80145</v>
+        <v>57725</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2559,21 +2554,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2583,10 +2578,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511485</v>
+        <v>510658</v>
       </c>
       <c r="R21" t="n">
-        <v>7106629</v>
+        <v>7106454</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2619,6 +2614,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2648,7 +2648,7 @@
         <v>128794498</v>
       </c>
       <c r="B22" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         <v>128794476</v>
       </c>
       <c r="B23" t="n">
-        <v>91892</v>
+        <v>91899</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2840,10 +2840,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128794515</v>
+        <v>128794525</v>
       </c>
       <c r="B24" t="n">
-        <v>91551</v>
+        <v>88937</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2851,21 +2851,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2875,10 +2875,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>511143</v>
+        <v>510696</v>
       </c>
       <c r="R24" t="n">
-        <v>7106625</v>
+        <v>7106461</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128794525</v>
+        <v>128794515</v>
       </c>
       <c r="B25" t="n">
-        <v>88930</v>
+        <v>91558</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2948,21 +2948,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>510696</v>
+        <v>511143</v>
       </c>
       <c r="R25" t="n">
-        <v>7106461</v>
+        <v>7106625</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128794486</v>
+        <v>128794511</v>
       </c>
       <c r="B27" t="n">
-        <v>91533</v>
+        <v>91558</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3147,21 +3147,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>510777</v>
+        <v>511450</v>
       </c>
       <c r="R27" t="n">
-        <v>7106379</v>
+        <v>7106469</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3233,10 +3233,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128794503</v>
+        <v>128794516</v>
       </c>
       <c r="B28" t="n">
-        <v>80144</v>
+        <v>79039</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3244,21 +3244,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>510694</v>
+        <v>511210</v>
       </c>
       <c r="R28" t="n">
-        <v>7106493</v>
+        <v>7106268</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3304,6 +3304,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3330,10 +3335,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128794511</v>
+        <v>128794503</v>
       </c>
       <c r="B29" t="n">
-        <v>91551</v>
+        <v>80144</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3341,21 +3346,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3365,10 +3370,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>511450</v>
+        <v>510694</v>
       </c>
       <c r="R29" t="n">
-        <v>7106469</v>
+        <v>7106493</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3427,10 +3432,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128794516</v>
+        <v>128794486</v>
       </c>
       <c r="B30" t="n">
-        <v>79039</v>
+        <v>91540</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3438,21 +3443,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3462,10 +3467,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>511210</v>
+        <v>510777</v>
       </c>
       <c r="R30" t="n">
-        <v>7106268</v>
+        <v>7106379</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3498,11 +3503,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3529,32 +3529,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128794502</v>
+        <v>128794497</v>
       </c>
       <c r="B31" t="n">
-        <v>80144</v>
+        <v>91995</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3564,10 +3564,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>510867</v>
+        <v>510812</v>
       </c>
       <c r="R31" t="n">
-        <v>7106619</v>
+        <v>7106615</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3626,32 +3626,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128794497</v>
+        <v>128794502</v>
       </c>
       <c r="B32" t="n">
-        <v>91988</v>
+        <v>80144</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3661,10 +3661,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>510812</v>
+        <v>510867</v>
       </c>
       <c r="R32" t="n">
-        <v>7106615</v>
+        <v>7106619</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3922,10 +3922,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128794489</v>
+        <v>128794504</v>
       </c>
       <c r="B35" t="n">
-        <v>57725</v>
+        <v>80144</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3933,21 +3933,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3957,10 +3957,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>510914</v>
+        <v>510707</v>
       </c>
       <c r="R35" t="n">
-        <v>7106330</v>
+        <v>7106493</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3993,11 +3993,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4024,10 +4019,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128794504</v>
+        <v>128794489</v>
       </c>
       <c r="B36" t="n">
-        <v>80144</v>
+        <v>57725</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4035,21 +4030,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4059,10 +4054,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>510707</v>
+        <v>510914</v>
       </c>
       <c r="R36" t="n">
-        <v>7106493</v>
+        <v>7106330</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4095,6 +4090,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4331,7 +4331,7 @@
         <v>128794513</v>
       </c>
       <c r="B39" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4522,10 +4522,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128794512</v>
+        <v>128794484</v>
       </c>
       <c r="B41" t="n">
-        <v>91551</v>
+        <v>91540</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4533,21 +4533,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4557,10 +4557,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>511307</v>
+        <v>510684</v>
       </c>
       <c r="R41" t="n">
-        <v>7106634</v>
+        <v>7106476</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4619,10 +4619,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128794484</v>
+        <v>128794510</v>
       </c>
       <c r="B42" t="n">
-        <v>91533</v>
+        <v>91554</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4630,21 +4630,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4654,10 +4654,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>510684</v>
+        <v>510841</v>
       </c>
       <c r="R42" t="n">
-        <v>7106476</v>
+        <v>7106597</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4716,10 +4716,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128794510</v>
+        <v>128794512</v>
       </c>
       <c r="B43" t="n">
-        <v>91547</v>
+        <v>91558</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4727,21 +4727,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4751,10 +4751,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>510841</v>
+        <v>511307</v>
       </c>
       <c r="R43" t="n">
-        <v>7106597</v>
+        <v>7106634</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4816,7 +4816,7 @@
         <v>128794526</v>
       </c>
       <c r="B44" t="n">
-        <v>89508</v>
+        <v>89515</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 31817-2025 artfynd.xlsx
+++ b/artfynd/A 31817-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128794508</v>
+        <v>128794507</v>
       </c>
       <c r="B2" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510782</v>
+        <v>510771</v>
       </c>
       <c r="R2" t="n">
-        <v>7106356</v>
+        <v>7106380</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128794507</v>
+        <v>128794508</v>
       </c>
       <c r="B3" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510771</v>
+        <v>510782</v>
       </c>
       <c r="R3" t="n">
-        <v>7106380</v>
+        <v>7106356</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,7 +877,7 @@
         <v>128794519</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>128794520</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1073,32 +1073,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128794477</v>
+        <v>128794499</v>
       </c>
       <c r="B6" t="n">
-        <v>91899</v>
+        <v>80146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2062</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510687</v>
+        <v>511149</v>
       </c>
       <c r="R6" t="n">
-        <v>7106478</v>
+        <v>7106300</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128794499</v>
+        <v>128794492</v>
       </c>
       <c r="B7" t="n">
-        <v>80144</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511149</v>
+        <v>510773</v>
       </c>
       <c r="R7" t="n">
-        <v>7106300</v>
+        <v>7106391</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1241,6 +1241,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,32 +1272,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128794492</v>
+        <v>128794477</v>
       </c>
       <c r="B8" t="n">
-        <v>57725</v>
+        <v>91901</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510773</v>
+        <v>510687</v>
       </c>
       <c r="R8" t="n">
-        <v>7106391</v>
+        <v>7106478</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1338,11 +1343,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1372,7 +1372,7 @@
         <v>128794485</v>
       </c>
       <c r="B9" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>128794479</v>
       </c>
       <c r="B10" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>128794480</v>
       </c>
       <c r="B11" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1660,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128794482</v>
+        <v>128794509</v>
       </c>
       <c r="B12" t="n">
-        <v>91540</v>
+        <v>91538</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1671,21 +1671,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>510816</v>
+        <v>510663</v>
       </c>
       <c r="R12" t="n">
-        <v>7106613</v>
+        <v>7106445</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128794481</v>
+        <v>128794478</v>
       </c>
       <c r="B13" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510842</v>
+        <v>511159</v>
       </c>
       <c r="R13" t="n">
-        <v>7106609</v>
+        <v>7106615</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128794478</v>
+        <v>128794481</v>
       </c>
       <c r="B14" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511159</v>
+        <v>510842</v>
       </c>
       <c r="R14" t="n">
-        <v>7106615</v>
+        <v>7106609</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128794501</v>
+        <v>128794482</v>
       </c>
       <c r="B15" t="n">
-        <v>80144</v>
+        <v>91542</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1962,21 +1962,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>511349</v>
+        <v>510816</v>
       </c>
       <c r="R15" t="n">
-        <v>7106644</v>
+        <v>7106613</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128794509</v>
+        <v>128794501</v>
       </c>
       <c r="B16" t="n">
-        <v>91536</v>
+        <v>80146</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,21 +2059,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>510663</v>
+        <v>511349</v>
       </c>
       <c r="R16" t="n">
-        <v>7106445</v>
+        <v>7106644</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2148,7 +2148,7 @@
         <v>128794506</v>
       </c>
       <c r="B17" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>128794524</v>
       </c>
       <c r="B18" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>128794488</v>
       </c>
       <c r="B19" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2446,10 +2446,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128794496</v>
+        <v>128794491</v>
       </c>
       <c r="B20" t="n">
-        <v>80145</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2457,21 +2457,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511485</v>
+        <v>510658</v>
       </c>
       <c r="R20" t="n">
-        <v>7106629</v>
+        <v>7106454</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2517,6 +2517,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2543,10 +2548,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128794491</v>
+        <v>128794496</v>
       </c>
       <c r="B21" t="n">
-        <v>57725</v>
+        <v>80147</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2554,21 +2559,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2578,10 +2583,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>510658</v>
+        <v>511485</v>
       </c>
       <c r="R21" t="n">
-        <v>7106454</v>
+        <v>7106629</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2614,11 +2619,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2648,7 +2648,7 @@
         <v>128794498</v>
       </c>
       <c r="B22" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         <v>128794476</v>
       </c>
       <c r="B23" t="n">
-        <v>91899</v>
+        <v>91901</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>128794525</v>
       </c>
       <c r="B24" t="n">
-        <v>88937</v>
+        <v>88939</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>128794515</v>
       </c>
       <c r="B25" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>128794517</v>
       </c>
       <c r="B26" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>128794511</v>
       </c>
       <c r="B27" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3233,10 +3233,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128794516</v>
+        <v>128794503</v>
       </c>
       <c r="B28" t="n">
-        <v>79039</v>
+        <v>80146</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3244,21 +3244,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>511210</v>
+        <v>510694</v>
       </c>
       <c r="R28" t="n">
-        <v>7106268</v>
+        <v>7106493</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3304,11 +3304,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3335,10 +3330,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128794503</v>
+        <v>128794486</v>
       </c>
       <c r="B29" t="n">
-        <v>80144</v>
+        <v>91542</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3346,21 +3341,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3370,10 +3365,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>510694</v>
+        <v>510777</v>
       </c>
       <c r="R29" t="n">
-        <v>7106493</v>
+        <v>7106379</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3432,10 +3427,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128794486</v>
+        <v>128794516</v>
       </c>
       <c r="B30" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3443,21 +3438,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3467,10 +3462,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>510777</v>
+        <v>511210</v>
       </c>
       <c r="R30" t="n">
-        <v>7106379</v>
+        <v>7106268</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3503,6 +3498,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3532,7 +3532,7 @@
         <v>128794497</v>
       </c>
       <c r="B31" t="n">
-        <v>91995</v>
+        <v>91997</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>128794502</v>
       </c>
       <c r="B32" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         <v>128794521</v>
       </c>
       <c r="B33" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>128794505</v>
       </c>
       <c r="B34" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>128794504</v>
       </c>
       <c r="B35" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>128794489</v>
       </c>
       <c r="B36" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>128794495</v>
       </c>
       <c r="B37" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         <v>128794500</v>
       </c>
       <c r="B38" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4328,10 +4328,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128794513</v>
+        <v>128794523</v>
       </c>
       <c r="B39" t="n">
-        <v>91558</v>
+        <v>79041</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4339,21 +4339,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4363,10 +4363,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>511247</v>
+        <v>510685</v>
       </c>
       <c r="R39" t="n">
-        <v>7106612</v>
+        <v>7106500</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4425,10 +4425,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128794523</v>
+        <v>128794513</v>
       </c>
       <c r="B40" t="n">
-        <v>79039</v>
+        <v>91560</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4436,21 +4436,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4460,10 +4460,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>510685</v>
+        <v>511247</v>
       </c>
       <c r="R40" t="n">
-        <v>7106500</v>
+        <v>7106612</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4522,10 +4522,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128794484</v>
+        <v>128794510</v>
       </c>
       <c r="B41" t="n">
-        <v>91540</v>
+        <v>91556</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4533,21 +4533,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4557,10 +4557,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>510684</v>
+        <v>510841</v>
       </c>
       <c r="R41" t="n">
-        <v>7106476</v>
+        <v>7106597</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4619,10 +4619,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128794510</v>
+        <v>128794484</v>
       </c>
       <c r="B42" t="n">
-        <v>91554</v>
+        <v>91542</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4630,21 +4630,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4654,10 +4654,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>510841</v>
+        <v>510684</v>
       </c>
       <c r="R42" t="n">
-        <v>7106597</v>
+        <v>7106476</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4719,7 +4719,7 @@
         <v>128794512</v>
       </c>
       <c r="B43" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>128794526</v>
       </c>
       <c r="B44" t="n">
-        <v>89515</v>
+        <v>89517</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 31817-2025 artfynd.xlsx
+++ b/artfynd/A 31817-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128794507</v>
+        <v>128794508</v>
       </c>
       <c r="B2" t="n">
         <v>80146</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510771</v>
+        <v>510782</v>
       </c>
       <c r="R2" t="n">
-        <v>7106380</v>
+        <v>7106356</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128794508</v>
+        <v>128794507</v>
       </c>
       <c r="B3" t="n">
         <v>80146</v>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510782</v>
+        <v>510771</v>
       </c>
       <c r="R3" t="n">
-        <v>7106356</v>
+        <v>7106380</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128794519</v>
+        <v>128794499</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511436</v>
+        <v>511149</v>
       </c>
       <c r="R4" t="n">
-        <v>7106614</v>
+        <v>7106300</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,7 +971,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128794520</v>
+        <v>128794519</v>
       </c>
       <c r="B5" t="n">
         <v>79041</v>
@@ -1011,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511309</v>
+        <v>511436</v>
       </c>
       <c r="R5" t="n">
-        <v>7106636</v>
+        <v>7106614</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,6 +1042,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128794499</v>
+        <v>128794520</v>
       </c>
       <c r="B6" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511149</v>
+        <v>511309</v>
       </c>
       <c r="R6" t="n">
-        <v>7106300</v>
+        <v>7106636</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128794492</v>
+        <v>128794477</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>91901</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510773</v>
+        <v>510687</v>
       </c>
       <c r="R7" t="n">
-        <v>7106391</v>
+        <v>7106478</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1241,11 +1241,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1272,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128794477</v>
+        <v>128794492</v>
       </c>
       <c r="B8" t="n">
-        <v>91901</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510687</v>
+        <v>510773</v>
       </c>
       <c r="R8" t="n">
-        <v>7106478</v>
+        <v>7106391</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1343,6 +1338,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1660,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128794509</v>
+        <v>128794501</v>
       </c>
       <c r="B12" t="n">
-        <v>91538</v>
+        <v>80146</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1671,21 +1671,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>510663</v>
+        <v>511349</v>
       </c>
       <c r="R12" t="n">
-        <v>7106445</v>
+        <v>7106644</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128794478</v>
+        <v>128794506</v>
       </c>
       <c r="B13" t="n">
-        <v>91542</v>
+        <v>80146</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511159</v>
+        <v>510758</v>
       </c>
       <c r="R13" t="n">
-        <v>7106615</v>
+        <v>7106421</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128794481</v>
+        <v>128794509</v>
       </c>
       <c r="B14" t="n">
-        <v>91542</v>
+        <v>91538</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>510842</v>
+        <v>510663</v>
       </c>
       <c r="R14" t="n">
-        <v>7106609</v>
+        <v>7106445</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128794501</v>
+        <v>128794481</v>
       </c>
       <c r="B16" t="n">
-        <v>80146</v>
+        <v>91542</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,21 +2059,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511349</v>
+        <v>510842</v>
       </c>
       <c r="R16" t="n">
-        <v>7106644</v>
+        <v>7106609</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,10 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128794506</v>
+        <v>128794478</v>
       </c>
       <c r="B17" t="n">
-        <v>80146</v>
+        <v>91542</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,21 +2156,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>510758</v>
+        <v>511159</v>
       </c>
       <c r="R17" t="n">
-        <v>7106421</v>
+        <v>7106615</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2242,10 +2242,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128794524</v>
+        <v>128794488</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2253,21 +2253,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>510700</v>
+        <v>510695</v>
       </c>
       <c r="R18" t="n">
-        <v>7106468</v>
+        <v>7106401</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Granska rikligt</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2344,10 +2344,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128794488</v>
+        <v>128794524</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2355,21 +2355,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>510695</v>
+        <v>510700</v>
       </c>
       <c r="R19" t="n">
-        <v>7106401</v>
+        <v>7106468</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2419,7 +2419,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Granska rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2446,10 +2446,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128794491</v>
+        <v>128794496</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2457,21 +2457,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>510658</v>
+        <v>511485</v>
       </c>
       <c r="R20" t="n">
-        <v>7106454</v>
+        <v>7106629</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2517,11 +2517,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2548,10 +2543,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128794496</v>
+        <v>128794491</v>
       </c>
       <c r="B21" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2559,21 +2554,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2583,10 +2578,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511485</v>
+        <v>510658</v>
       </c>
       <c r="R21" t="n">
-        <v>7106629</v>
+        <v>7106454</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2619,6 +2614,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2840,10 +2840,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128794525</v>
+        <v>128794517</v>
       </c>
       <c r="B24" t="n">
-        <v>88939</v>
+        <v>79041</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2851,21 +2851,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2875,10 +2875,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>510696</v>
+        <v>511489</v>
       </c>
       <c r="R24" t="n">
-        <v>7106461</v>
+        <v>7106495</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2911,6 +2911,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2937,10 +2942,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128794515</v>
+        <v>128794525</v>
       </c>
       <c r="B25" t="n">
-        <v>91560</v>
+        <v>88939</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2948,21 +2953,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2972,10 +2977,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>511143</v>
+        <v>510696</v>
       </c>
       <c r="R25" t="n">
-        <v>7106625</v>
+        <v>7106461</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3034,10 +3039,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128794517</v>
+        <v>128794515</v>
       </c>
       <c r="B26" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3045,21 +3050,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3069,10 +3074,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>511489</v>
+        <v>511143</v>
       </c>
       <c r="R26" t="n">
-        <v>7106495</v>
+        <v>7106625</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3105,11 +3110,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3136,10 +3136,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128794511</v>
+        <v>128794516</v>
       </c>
       <c r="B27" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3147,21 +3147,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>511450</v>
+        <v>511210</v>
       </c>
       <c r="R27" t="n">
-        <v>7106469</v>
+        <v>7106268</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3207,6 +3207,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3233,10 +3238,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128794503</v>
+        <v>128794511</v>
       </c>
       <c r="B28" t="n">
-        <v>80146</v>
+        <v>91560</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3244,21 +3249,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3268,10 +3273,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>510694</v>
+        <v>511450</v>
       </c>
       <c r="R28" t="n">
-        <v>7106493</v>
+        <v>7106469</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3427,10 +3432,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128794516</v>
+        <v>128794503</v>
       </c>
       <c r="B30" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3438,21 +3443,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3462,10 +3467,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>511210</v>
+        <v>510694</v>
       </c>
       <c r="R30" t="n">
-        <v>7106268</v>
+        <v>7106493</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3498,11 +3503,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3723,10 +3723,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128794521</v>
+        <v>128794505</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3734,21 +3734,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>511134</v>
+        <v>510689</v>
       </c>
       <c r="R33" t="n">
-        <v>7106628</v>
+        <v>7106463</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3794,11 +3794,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3825,10 +3820,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128794505</v>
+        <v>128794521</v>
       </c>
       <c r="B34" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3836,21 +3831,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3860,10 +3855,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>510689</v>
+        <v>511134</v>
       </c>
       <c r="R34" t="n">
-        <v>7106463</v>
+        <v>7106628</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3896,6 +3891,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4328,10 +4328,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128794523</v>
+        <v>128794513</v>
       </c>
       <c r="B39" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4339,21 +4339,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4363,10 +4363,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>510685</v>
+        <v>511247</v>
       </c>
       <c r="R39" t="n">
-        <v>7106500</v>
+        <v>7106612</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4425,10 +4425,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128794513</v>
+        <v>128794523</v>
       </c>
       <c r="B40" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4436,21 +4436,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4460,10 +4460,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>511247</v>
+        <v>510685</v>
       </c>
       <c r="R40" t="n">
-        <v>7106612</v>
+        <v>7106500</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4522,10 +4522,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128794510</v>
+        <v>128794484</v>
       </c>
       <c r="B41" t="n">
-        <v>91556</v>
+        <v>91542</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4533,21 +4533,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4557,10 +4557,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>510841</v>
+        <v>510684</v>
       </c>
       <c r="R41" t="n">
-        <v>7106597</v>
+        <v>7106476</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4619,10 +4619,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128794484</v>
+        <v>128794510</v>
       </c>
       <c r="B42" t="n">
-        <v>91542</v>
+        <v>91556</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4630,21 +4630,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4654,10 +4654,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>510684</v>
+        <v>510841</v>
       </c>
       <c r="R42" t="n">
-        <v>7106476</v>
+        <v>7106597</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>

--- a/artfynd/A 31817-2025 artfynd.xlsx
+++ b/artfynd/A 31817-2025 artfynd.xlsx
@@ -1660,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128794501</v>
+        <v>128794509</v>
       </c>
       <c r="B12" t="n">
-        <v>80146</v>
+        <v>91538</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1671,21 +1671,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511349</v>
+        <v>510663</v>
       </c>
       <c r="R12" t="n">
-        <v>7106644</v>
+        <v>7106445</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128794506</v>
+        <v>128794482</v>
       </c>
       <c r="B13" t="n">
-        <v>80146</v>
+        <v>91542</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510758</v>
+        <v>510816</v>
       </c>
       <c r="R13" t="n">
-        <v>7106421</v>
+        <v>7106613</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128794509</v>
+        <v>128794481</v>
       </c>
       <c r="B14" t="n">
-        <v>91538</v>
+        <v>91542</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>510663</v>
+        <v>510842</v>
       </c>
       <c r="R14" t="n">
-        <v>7106445</v>
+        <v>7106609</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1951,7 +1951,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128794482</v>
+        <v>128794478</v>
       </c>
       <c r="B15" t="n">
         <v>91542</v>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>510816</v>
+        <v>511159</v>
       </c>
       <c r="R15" t="n">
-        <v>7106613</v>
+        <v>7106615</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128794481</v>
+        <v>128794501</v>
       </c>
       <c r="B16" t="n">
-        <v>91542</v>
+        <v>80146</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,21 +2059,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>510842</v>
+        <v>511349</v>
       </c>
       <c r="R16" t="n">
-        <v>7106609</v>
+        <v>7106644</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,10 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128794478</v>
+        <v>128794506</v>
       </c>
       <c r="B17" t="n">
-        <v>91542</v>
+        <v>80146</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,21 +2156,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511159</v>
+        <v>510758</v>
       </c>
       <c r="R17" t="n">
-        <v>7106615</v>
+        <v>7106421</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2242,10 +2242,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128794488</v>
+        <v>128794524</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2253,21 +2253,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>510695</v>
+        <v>510700</v>
       </c>
       <c r="R18" t="n">
-        <v>7106401</v>
+        <v>7106468</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Granska rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2344,10 +2344,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128794524</v>
+        <v>128794488</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2355,21 +2355,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>510700</v>
+        <v>510695</v>
       </c>
       <c r="R19" t="n">
-        <v>7106468</v>
+        <v>7106401</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2419,7 +2419,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Granska rikligt</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -4328,10 +4328,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128794513</v>
+        <v>128794523</v>
       </c>
       <c r="B39" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4339,21 +4339,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4363,10 +4363,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>511247</v>
+        <v>510685</v>
       </c>
       <c r="R39" t="n">
-        <v>7106612</v>
+        <v>7106500</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4425,10 +4425,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128794523</v>
+        <v>128794513</v>
       </c>
       <c r="B40" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4436,21 +4436,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4460,10 +4460,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>510685</v>
+        <v>511247</v>
       </c>
       <c r="R40" t="n">
-        <v>7106500</v>
+        <v>7106612</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>

--- a/artfynd/A 31817-2025 artfynd.xlsx
+++ b/artfynd/A 31817-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128794508</v>
+        <v>128794507</v>
       </c>
       <c r="B2" t="n">
         <v>80146</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510782</v>
+        <v>510771</v>
       </c>
       <c r="R2" t="n">
-        <v>7106356</v>
+        <v>7106380</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128794507</v>
+        <v>128794508</v>
       </c>
       <c r="B3" t="n">
         <v>80146</v>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510771</v>
+        <v>510782</v>
       </c>
       <c r="R3" t="n">
-        <v>7106380</v>
+        <v>7106356</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128794499</v>
+        <v>128794492</v>
       </c>
       <c r="B4" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511149</v>
+        <v>510773</v>
       </c>
       <c r="R4" t="n">
-        <v>7106300</v>
+        <v>7106391</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1170,32 +1175,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128794477</v>
+        <v>128794499</v>
       </c>
       <c r="B7" t="n">
-        <v>91901</v>
+        <v>80146</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2062</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510687</v>
+        <v>511149</v>
       </c>
       <c r="R7" t="n">
-        <v>7106478</v>
+        <v>7106300</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,32 +1272,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128794492</v>
+        <v>128794477</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>91910</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510773</v>
+        <v>510687</v>
       </c>
       <c r="R8" t="n">
-        <v>7106391</v>
+        <v>7106478</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1338,11 +1343,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1372,7 +1372,7 @@
         <v>128794485</v>
       </c>
       <c r="B9" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>128794479</v>
       </c>
       <c r="B10" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>128794480</v>
       </c>
       <c r="B11" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1660,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128794509</v>
+        <v>128794501</v>
       </c>
       <c r="B12" t="n">
-        <v>91538</v>
+        <v>80146</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1671,21 +1671,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>510663</v>
+        <v>511349</v>
       </c>
       <c r="R12" t="n">
-        <v>7106445</v>
+        <v>7106644</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128794482</v>
+        <v>128794506</v>
       </c>
       <c r="B13" t="n">
-        <v>91542</v>
+        <v>80146</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510816</v>
+        <v>510758</v>
       </c>
       <c r="R13" t="n">
-        <v>7106613</v>
+        <v>7106421</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128794481</v>
+        <v>128794509</v>
       </c>
       <c r="B14" t="n">
-        <v>91542</v>
+        <v>91536</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>510842</v>
+        <v>510663</v>
       </c>
       <c r="R14" t="n">
-        <v>7106609</v>
+        <v>7106445</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128794478</v>
+        <v>128794482</v>
       </c>
       <c r="B15" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>511159</v>
+        <v>510816</v>
       </c>
       <c r="R15" t="n">
-        <v>7106615</v>
+        <v>7106613</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128794501</v>
+        <v>128794481</v>
       </c>
       <c r="B16" t="n">
-        <v>80146</v>
+        <v>91540</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,21 +2059,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511349</v>
+        <v>510842</v>
       </c>
       <c r="R16" t="n">
-        <v>7106644</v>
+        <v>7106609</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,10 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128794506</v>
+        <v>128794478</v>
       </c>
       <c r="B17" t="n">
-        <v>80146</v>
+        <v>91540</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,21 +2156,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>510758</v>
+        <v>511159</v>
       </c>
       <c r="R17" t="n">
-        <v>7106421</v>
+        <v>7106615</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2446,10 +2446,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128794496</v>
+        <v>128794491</v>
       </c>
       <c r="B20" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2457,21 +2457,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511485</v>
+        <v>510658</v>
       </c>
       <c r="R20" t="n">
-        <v>7106629</v>
+        <v>7106454</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2517,6 +2517,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2543,10 +2548,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128794491</v>
+        <v>128794496</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2554,21 +2559,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2578,10 +2583,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>510658</v>
+        <v>511485</v>
       </c>
       <c r="R21" t="n">
-        <v>7106454</v>
+        <v>7106629</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2614,11 +2619,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2648,7 +2648,7 @@
         <v>128794498</v>
       </c>
       <c r="B22" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         <v>128794476</v>
       </c>
       <c r="B23" t="n">
-        <v>91901</v>
+        <v>91910</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2840,10 +2840,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128794517</v>
+        <v>128794525</v>
       </c>
       <c r="B24" t="n">
-        <v>79041</v>
+        <v>88940</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2851,21 +2851,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2875,10 +2875,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>511489</v>
+        <v>510696</v>
       </c>
       <c r="R24" t="n">
-        <v>7106495</v>
+        <v>7106461</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2911,11 +2911,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2942,10 +2937,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128794525</v>
+        <v>128794515</v>
       </c>
       <c r="B25" t="n">
-        <v>88939</v>
+        <v>91558</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2953,21 +2948,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2977,10 +2972,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>510696</v>
+        <v>511143</v>
       </c>
       <c r="R25" t="n">
-        <v>7106461</v>
+        <v>7106625</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3039,10 +3034,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128794515</v>
+        <v>128794517</v>
       </c>
       <c r="B26" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3050,21 +3045,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3074,10 +3069,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>511143</v>
+        <v>511489</v>
       </c>
       <c r="R26" t="n">
-        <v>7106625</v>
+        <v>7106495</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3110,6 +3105,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3136,10 +3136,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128794516</v>
+        <v>128794503</v>
       </c>
       <c r="B27" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3147,21 +3147,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>511210</v>
+        <v>510694</v>
       </c>
       <c r="R27" t="n">
-        <v>7106268</v>
+        <v>7106493</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3207,11 +3207,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3238,10 +3233,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128794511</v>
+        <v>128794486</v>
       </c>
       <c r="B28" t="n">
-        <v>91560</v>
+        <v>91540</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3249,21 +3244,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3273,10 +3268,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>511450</v>
+        <v>510777</v>
       </c>
       <c r="R28" t="n">
-        <v>7106469</v>
+        <v>7106379</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3335,10 +3330,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128794486</v>
+        <v>128794511</v>
       </c>
       <c r="B29" t="n">
-        <v>91542</v>
+        <v>91558</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3346,21 +3341,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3370,10 +3365,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>510777</v>
+        <v>511450</v>
       </c>
       <c r="R29" t="n">
-        <v>7106379</v>
+        <v>7106469</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3432,10 +3427,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128794503</v>
+        <v>128794516</v>
       </c>
       <c r="B30" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3443,21 +3438,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3467,10 +3462,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>510694</v>
+        <v>511210</v>
       </c>
       <c r="R30" t="n">
-        <v>7106493</v>
+        <v>7106268</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3503,6 +3498,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3529,32 +3529,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128794497</v>
+        <v>128794502</v>
       </c>
       <c r="B31" t="n">
-        <v>91997</v>
+        <v>80146</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3564,10 +3564,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>510812</v>
+        <v>510867</v>
       </c>
       <c r="R31" t="n">
-        <v>7106615</v>
+        <v>7106619</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3626,32 +3626,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128794502</v>
+        <v>128794497</v>
       </c>
       <c r="B32" t="n">
-        <v>80146</v>
+        <v>91992</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3661,10 +3661,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>510867</v>
+        <v>510812</v>
       </c>
       <c r="R32" t="n">
-        <v>7106619</v>
+        <v>7106615</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3723,10 +3723,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128794505</v>
+        <v>128794521</v>
       </c>
       <c r="B33" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3734,21 +3734,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>510689</v>
+        <v>511134</v>
       </c>
       <c r="R33" t="n">
-        <v>7106463</v>
+        <v>7106628</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3794,6 +3794,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3820,10 +3825,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128794521</v>
+        <v>128794505</v>
       </c>
       <c r="B34" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3831,21 +3836,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3855,10 +3860,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>511134</v>
+        <v>510689</v>
       </c>
       <c r="R34" t="n">
-        <v>7106628</v>
+        <v>7106463</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3891,11 +3896,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3922,10 +3922,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128794504</v>
+        <v>128794489</v>
       </c>
       <c r="B35" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3933,21 +3933,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3957,10 +3957,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>510707</v>
+        <v>510914</v>
       </c>
       <c r="R35" t="n">
-        <v>7106493</v>
+        <v>7106330</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3993,6 +3993,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4019,10 +4024,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128794489</v>
+        <v>128794504</v>
       </c>
       <c r="B36" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4030,21 +4035,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4054,10 +4059,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>510914</v>
+        <v>510707</v>
       </c>
       <c r="R36" t="n">
-        <v>7106330</v>
+        <v>7106493</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4090,11 +4095,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4328,10 +4328,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128794523</v>
+        <v>128794513</v>
       </c>
       <c r="B39" t="n">
-        <v>79041</v>
+        <v>91558</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4339,21 +4339,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4363,10 +4363,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>510685</v>
+        <v>511247</v>
       </c>
       <c r="R39" t="n">
-        <v>7106500</v>
+        <v>7106612</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4425,10 +4425,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128794513</v>
+        <v>128794523</v>
       </c>
       <c r="B40" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4436,21 +4436,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4460,10 +4460,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>511247</v>
+        <v>510685</v>
       </c>
       <c r="R40" t="n">
-        <v>7106612</v>
+        <v>7106500</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4525,7 +4525,7 @@
         <v>128794484</v>
       </c>
       <c r="B41" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>128794510</v>
       </c>
       <c r="B42" t="n">
-        <v>91556</v>
+        <v>91554</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>128794512</v>
       </c>
       <c r="B43" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>128794526</v>
       </c>
       <c r="B44" t="n">
-        <v>89517</v>
+        <v>89518</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
